--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,31 +736,31 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>186.2</v>
+        <v>29.2</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>28.8</v>
+        <v>29.7</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>18.2</v>
+        <v>2.7</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>9.9</v>
+        <v>22.9</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>20.2</v>
@@ -769,25 +769,25 @@
         <v>20.1</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>99</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>28.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.8</v>
+        <v>27.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>168.9</v>
+        <v>683.9</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>12.2</v>
@@ -796,17 +796,15 @@
         <v>25.2</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>811.8</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>81.8</v>
+      </c>
+      <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -821,25 +819,21 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>403.5</v>
+        <v>43.5</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n">
-        <v>25.4</v>
+        <v>5.1</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n">
-        <v>32.5</v>
+        <v>3.5</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>5.5</v>
@@ -847,51 +841,49 @@
       <c r="K5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="n">
-        <v>18.9</v>
+      <c r="L5" s="8" t="n">
+        <v>82.90000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>28.6</v>
+        <v>26.6</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>99</v>
+        <v>292</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q5" s="3" t="n">
-        <v>32.6</v>
+      <c r="Q5" s="8" t="n">
+        <v>26.6</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>25.4</v>
+        <v>2.5</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>156.6</v>
+        <v>56.6</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>27.2</v>
+        <v>26</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="X5" s="8" t="n">
-        <v>27.8</v>
+        <v>22.8</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="Z5" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
+        <v>25.8</v>
+      </c>
+      <c r="Z5" s="3" t="n"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -906,13 +898,17 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>422.3</v>
+        <v>22.3</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>18.8</v>
+        <v>34.8</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+13
+</t>
+        </is>
       </c>
       <c r="F6" s="3" t="n">
         <v>26.5</v>
@@ -921,13 +917,13 @@
         <v>15.4</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>17.2</v>
+        <v>7.7</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>22.6</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -942,7 +938,7 @@
         <v>23.3</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>0</v>
@@ -954,28 +950,28 @@
         <v>25.7</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>28.6</v>
+        <v>22.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>55.2</v>
+        <v>52.8</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>28.7</v>
+        <v>2.8</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>26.1</v>
+        <v>6.4</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>22.2</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>4.1</v>
+        <v>13.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -990,75 +986,73 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>4335.1</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>34.7</v>
-      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">486860108728
+171171808
+</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n">
-        <v>19.3</v>
+        <v>12.3</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>43.3</v>
+        <v>4.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>35.1</v>
+        <v>26.1</v>
+      </c>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>34.2</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>25.5</v>
+        <v>22.5</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>27.1</v>
+        <v>22.1</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>50.6</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>26.5</v>
+        <v>20.7</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>24.4</v>
+        <v>24.9</v>
+      </c>
+      <c r="W7" s="8" t="n">
+        <v>26.1</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="Y7" s="3" t="n">
         <v>66.2</v>
       </c>
+      <c r="Y7" s="3" t="n"/>
       <c r="Z7" s="3" t="n">
         <v>13.8</v>
       </c>
@@ -1076,10 +1070,10 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>299</v>
+        <v>292.6</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>344.1</v>
+        <v>34.8</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>80.59999999999999</v>
@@ -1088,40 +1082,40 @@
         <v>27.6</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>119</v>
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>30.9</v>
+        <v>36.9</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>21</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="N8" s="8" t="n">
-        <v>40.9</v>
+        <v>26.6</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>24</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>96.5</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Q8" s="8" t="n">
-        <v>21.4</v>
+        <v>0.8</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>24.4</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>25.1</v>
@@ -1130,22 +1124,22 @@
         <v>98</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>10.4</v>
+        <v>6.5</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>22.2</v>
+        <v>4.9</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>21.9</v>
+        <v>4.9</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>26.1</v>
+        <v>2.3</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0.6</v>
+        <v>20.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1161,13 +1155,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1783.5</v>
+        <v>783.5</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>164.8</v>
+        <v>161.8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>96.90000000000001</v>
+        <v>962.9</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>130.8</v>
@@ -1176,60 +1170,60 @@
         <v>67.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>27.5</v>
+        <v>278.5</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>30.9</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>100.2</v>
+        <v>10.2</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>9292.6</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>115.8</v>
+        <v>18.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1894.5</v>
+        <v>94.5</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>149.6</v>
+        <v>49.6</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>121.9</v>
+        <v>121.2</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>135.7</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>229.9</v>
+        <v>2292.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>81</v>
+        <v>6.4</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>132.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>116.8</v>
+        <v>133.5</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>133.5</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>388.8</v>
-      </c>
-      <c r="Z9" s="3" t="n"/>
+        <v>26.1</v>
+      </c>
+      <c r="Y9" s="3" t="n"/>
+      <c r="Z9" s="3" t="n">
+        <v>6.6</v>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1244,22 +1238,25 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>356.7</v>
+        <v>36.7</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>33</v>
+        <v>33.9</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>19.4</v>
+        <v>1.4</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>13.6</v>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 36
+</t>
+        </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>17.9</v>
+        <v>7.9</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>3.3</v>
@@ -1267,51 +1264,53 @@
       <c r="J10" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K10" s="3" t="n"/>
+      <c r="K10" s="3" t="n">
+        <v>7.1</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>20</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="N10" s="8" t="n">
-        <v>23.2</v>
+        <v>9.9</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>22.9</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="R10" s="8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="R10" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>27.1</v>
+        <v>2.1</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="V10" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="W10" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="W10" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="X10" s="3" t="n">
-        <v>26.7</v>
+      <c r="X10" s="8" t="n">
+        <v>88.8</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>77.8</v>
+        <v>7.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>41.6</v>
+        <v>4.6</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1329,72 +1328,70 @@
       <c r="C11" s="3" t="n">
         <v>265.6</v>
       </c>
-      <c r="D11" s="3" t="n">
-        <v>20.1</v>
+      <c r="D11" s="8" t="n">
+        <v>60.1</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>19.8</v>
+        <v>2.8</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>24.9</v>
+        <v>245.9</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>86.59999999999999</v>
+        <v>18.1</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>82.8</v>
+        <v>4.8</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>21.2</v>
+        <v>24.2</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="N11" s="8" t="n">
-        <v>124.5</v>
+      <c r="N11" s="3" t="n">
+        <v>4.5</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>92.3</v>
+        <v>23.3</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q11" s="8" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="R11" s="8" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="S11" s="8" t="n">
+      <c r="Q11" s="3" t="n">
+        <v>994.9</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="S11" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="W11" s="8" t="n">
-        <v>24.9</v>
+        <v>66</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>2.7</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>84</v>
-      </c>
+        <v>340.3</v>
+      </c>
+      <c r="Y11" s="3" t="n"/>
       <c r="Z11" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
@@ -1412,7 +1409,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>347.1</v>
+        <v>32.1</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>31.8</v>
@@ -1421,10 +1418,14 @@
         <v>22.6</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>2.2</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+191
+</t>
+        </is>
       </c>
       <c r="H12" s="3" t="n">
         <v>21.2</v>
@@ -1432,11 +1433,11 @@
       <c r="I12" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="J12" s="8" t="n">
-        <v>44.6</v>
+      <c r="J12" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>23.3</v>
@@ -1445,43 +1446,47 @@
         <v>23</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>27.9</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>0.5</v>
+        <v>7.8</v>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+711
+</t>
+        </is>
       </c>
       <c r="Q12" s="3" t="n">
         <v>31.8</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>24.9</v>
+        <v>4.9</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>57.8</v>
+        <v>20.6</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>19.8</v>
+        <v>3.8</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="W12" s="8" t="n">
-        <v>24.6</v>
+        <v>27.1</v>
+      </c>
+      <c r="W12" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>28.8</v>
+        <v>3.1</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>76.7</v>
+        <v>2292.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>5.7</v>
+        <v>57.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1497,34 +1502,34 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1428.6</v>
+        <v>122.6</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>32.8</v>
+        <v>1.2</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>20.4</v>
+        <v>0.2</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>96.59999999999999</v>
+        <v>26.6</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>19.9</v>
+        <v>1.9</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="8" t="n">
-        <v>22.1</v>
+      <c r="L13" s="3" t="n">
+        <v>2.1</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>21.9</v>
@@ -1533,40 +1538,40 @@
         <v>26.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>10.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>32.6</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>24.6</v>
+        <v>4.6</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>52.7</v>
+        <v>7.8</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v>28</v>
+        <v>33.2</v>
+      </c>
+      <c r="V13" s="3" t="n">
+        <v>7.9</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>29.3</v>
+        <v>24.6</v>
+      </c>
+      <c r="X13" s="8" t="n">
+        <v>72.7</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>77.59999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1582,13 +1587,13 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>190.3</v>
+        <v>90.3</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>21.9</v>
+        <v>60.7</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>12.9</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>26.3</v>
@@ -1597,22 +1602,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>20.3</v>
+        <v>26.3</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>52.1</v>
+        <v>2.1</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>22.4</v>
+        <v>0.2</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>22.1</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>26.4</v>
@@ -1621,31 +1626,29 @@
         <v>97.3</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>22.4</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>24.2</v>
+        <v>4.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>89</v>
+        <v>52.7</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>21.6</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="W14" s="3" t="n"/>
       <c r="X14" s="3" t="n">
-        <v>25.5</v>
+        <v>834.3</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>96</v>
@@ -1667,22 +1670,22 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>359.6</v>
+        <v>35.6</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>32.5</v>
       </c>
-      <c r="E15" s="8" t="n">
-        <v>8.800000000000001</v>
+      <c r="E15" s="3" t="n">
+        <v>21.8</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>26.7</v>
       </c>
-      <c r="G15" s="8" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>419.6</v>
+      <c r="G15" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>2.4</v>
@@ -1691,10 +1694,10 @@
         <v>3.9</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>25.9</v>
+        <v>25.2</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>21.6</v>
+        <v>4.6</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>21.6</v>
@@ -1703,7 +1706,7 @@
         <v>25.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>180</v>
+        <v>1006</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0</v>
@@ -1715,25 +1718,25 @@
         <v>25.8</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>89.2</v>
+        <v>29.2</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>61.7</v>
+        <v>82</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>28.7</v>
+        <v>2</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>24.8</v>
+        <v>26.8</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>28.8</v>
+        <v>25.5</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>73.09999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>0.9</v>
@@ -1752,13 +1755,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1591.2</v>
+        <v>1599.2</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0</v>
+        <v>152.9</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>105.5</v>
+        <v>15.5</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>131.7</v>
@@ -1767,56 +1770,62 @@
         <v>52.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>99.2</v>
+        <v>392.2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
+      <c r="K16" s="3" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>10.6</v>
+      </c>
       <c r="M16" s="3" t="n">
-        <v>109.5</v>
+        <v>19.5</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>130.7</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>490.1</v>
+        <v>20.1</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>148.7</v>
+        <v>48.2</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>121.9</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>136.1</v>
+        <v>36.1</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>331.8</v>
+        <v>61.7</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>26.6</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>133.7</v>
+        <v>28.7</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>120.7</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>142.5</v>
+        <v>28.8</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>407.4</v>
-      </c>
-      <c r="Z16" s="3" t="n"/>
+        <v>47.6</v>
+      </c>
+      <c r="Z16" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1831,19 +1840,19 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>318.2</v>
+        <v>3418.2</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>31.6</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>21.1</v>
+        <v>24.1</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>26.3</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>10.5</v>
+        <v>1.5</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>19.8</v>
@@ -1857,8 +1866,8 @@
       <c r="K17" s="3" t="n">
         <v>36.8</v>
       </c>
-      <c r="L17" s="8" t="n">
-        <v>10.6</v>
+      <c r="L17" s="3" t="n">
+        <v>22.1</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>21.9</v>
@@ -1867,40 +1876,40 @@
         <v>26.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P17" s="8" t="n">
-        <v>10.4</v>
+        <v>2</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>4.1</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>29.7</v>
+        <v>2.7</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>24.4</v>
+        <v>4.4</v>
       </c>
       <c r="S17" s="8" t="n">
-        <v>72.2</v>
+        <v>36.4</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>15.3</v>
+        <v>331.8</v>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v>45.3</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>26.7</v>
+        <v>33.7</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="X17" s="3" t="n">
-        <v>28.5</v>
+        <v>24.1</v>
+      </c>
+      <c r="X17" s="8" t="n">
+        <v>42.5</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>81.5</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>6.9</v>
+        <v>34.4</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1916,7 +1925,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>368</v>
+        <v>368.6</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>32.1</v>
@@ -1924,22 +1933,24 @@
       <c r="E18" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>20.4</v>
+        <v>1.9</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>6.4</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K18" s="3" t="n"/>
+        <v>4.1</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>7.6</v>
+      </c>
       <c r="L18" s="3" t="n">
         <v>22.1</v>
       </c>
@@ -1947,10 +1958,10 @@
         <v>21.1</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>24.8</v>
+        <v>4.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>92.3</v>
+        <v>97.3</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
@@ -1958,32 +1969,32 @@
       <c r="Q18" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="8" t="n">
+      <c r="R18" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>27.7</v>
+        <v>0.3</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="U18" s="8" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="U18" s="3" t="n">
         <v>20</v>
       </c>
       <c r="V18" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="W18" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X18" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="W18" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X18" s="3" t="n">
-        <v>27.9</v>
-      </c>
       <c r="Y18" s="3" t="n">
-        <v>71.7</v>
+        <v>119</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>1.1</v>
+        <v>6.9</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1999,13 +2010,13 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>265.6</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>26.3</v>
@@ -2014,7 +2025,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>21.4</v>
+        <v>2.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.6</v>
@@ -2023,52 +2034,56 @@
         <v>2.8</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>10.4</v>
+        <v>7.6</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>21.4</v>
+        <v>2.3</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>26.3</v>
+        <v>2</v>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">662
+1254
+</t>
+        </is>
       </c>
       <c r="O19" s="3" t="n">
-        <v>97.59999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>29.9</v>
+        <v>1.6</v>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <v>92.90000000000001</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>26</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>31.1</v>
+        <v>7.7</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>73.7</v>
+        <v>58</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v>24.3</v>
+        <v>1</v>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v>8.5</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>22.9</v>
+        <v>2.1</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>21.4</v>
+        <v>29</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>22</v>
+        <v>2.2</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2089,14 +2104,14 @@
       <c r="D20" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>21.5</v>
+      <c r="E20" s="8" t="n">
+        <v>41.5</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>26.5</v>
+        <v>24.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>9.9</v>
+        <v>29.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>20.6</v>
@@ -2105,55 +2120,59 @@
         <v>2.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>22.3</v>
+        <v>21.6</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>25.4</v>
+        <v>2.4</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">662
+1254
+</t>
+        </is>
       </c>
       <c r="O20" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.4</v>
+        <v>30.4</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>30.7</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>24.8</v>
+        <v>21.8</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>27.5</v>
+        <v>31.1</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>62.3</v>
+        <v>3.2</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>27.3</v>
+        <v>26.3</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>23.8</v>
+        <v>2.9</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>27.2</v>
+        <v>2.3</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>22</v>
+        <v>9.1</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>9.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2175,10 +2194,10 @@
         <v>30.7</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>21.2</v>
+        <v>22.2</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>25.9</v>
+        <v>24.5</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>9.5</v>
@@ -2193,7 +2212,7 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>21.6</v>
@@ -2202,10 +2221,10 @@
         <v>21.5</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>25.6</v>
+        <v>2.6</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0.2</v>
@@ -2217,29 +2236,27 @@
         <v>26.2</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>31.2</v>
+        <v>27.5</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>71.2</v>
+        <v>6.3</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X21" s="3" t="n">
-        <v>28.9</v>
+        <v>7.3</v>
+      </c>
+      <c r="W21" s="8" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="X21" s="8" t="n">
+        <v>25</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>772.3</v>
-      </c>
-      <c r="Z21" s="3" t="n">
-        <v>8.4</v>
-      </c>
+        <v>28.4</v>
+      </c>
+      <c r="Z21" s="3" t="n"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -2263,13 +2280,13 @@
         <v>21.1</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>19.8</v>
+        <v>12.8</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>2.5</v>
@@ -2278,19 +2295,19 @@
         <v>4.3</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="8" t="n">
-        <v>21.6</v>
+        <v>2.7</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>21.3</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>24.7</v>
+        <v>2.4</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>92.5</v>
+        <v>7.5</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.4</v>
@@ -2302,29 +2319,27 @@
         <v>25.9</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>89.3</v>
+        <v>31.2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>19.2</v>
+        <v>212.6</v>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v>92.2</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>26.5</v>
+        <v>4.1</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>24.6</v>
+        <v>4.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>29.7</v>
+        <v>8.9</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="Z22" s="3" t="n">
-        <v>4.9</v>
-      </c>
+        <v>72.3</v>
+      </c>
+      <c r="Z22" s="3" t="n"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -2339,22 +2354,30 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1739.6</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>2.2</v>
+        <v>732.6</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">422999227
+1149 6
+</t>
+        </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3.7</v>
+        <v>107.2</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>132.4</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>19.8</v>
+        <v>56.3</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4574532851
+12818
+</t>
+        </is>
       </c>
       <c r="I23" s="3" t="n">
         <v>10.9</v>
@@ -2363,52 +2386,56 @@
         <v>19.3</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>7.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>7.7</v>
+        <v>18.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>126.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1489.4</v>
+        <v>48.9</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>155.7</v>
+        <v>55.7</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>128.1</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1146.8</v>
+        <v>89.3</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>395.7</v>
+        <v>6.5</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>792.4</v>
+        <v>2.4</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>134.4</v>
+        <v>6.5</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>120.3</v>
+        <v>24.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>1408.1</v>
+        <v>29.7</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>3940.4</v>
-      </c>
-      <c r="Z23" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>26</v>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+78
+</t>
+        </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2424,76 +2451,80 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>343.9</v>
+        <v>4.2</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>31.5</v>
+        <v>57.5</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>10.1</v>
+        <v>1.1</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>1.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>3.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="L24" s="8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="M24" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="N24" s="8" t="n">
-        <v>26.8</v>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>5.4</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>97.90000000000001</v>
+        <v>27.3</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>31.1</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>25.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>29.4</v>
+        <v>46.8</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>32.5</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="V24" s="3" t="n">
-        <v>26.9</v>
+        <v>15.8</v>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v>31.4</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>24.1</v>
+        <v>20.3</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>22.2</v>
+        <v>40.8</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>79.8</v>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v>7.3</v>
+        <v>399</v>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+78
+</t>
+        </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2509,10 +2540,10 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>106.7</v>
+        <v>6.7</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>26.3</v>
+        <v>31.5</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>20.6</v>
@@ -2521,31 +2552,39 @@
         <v>23.5</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="I25" s="3" t="n">
-        <v>2.2</v>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24127
+210
+</t>
+        </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>21.6</v>
+        <v>2.4</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>21.4</v>
+        <v>986.1</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>97.90000000000001</v>
+        <v>26.7</v>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">779717
+1791818
+</t>
+        </is>
       </c>
       <c r="P25" s="3" t="n">
         <v>0.7</v>
@@ -2553,33 +2592,35 @@
       <c r="Q25" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="R25" s="8" t="n">
-        <v>146.1</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>28.7</v>
+      <c r="R25" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7783
+181186
+</t>
+        </is>
       </c>
       <c r="T25" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>654.1</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>5.3</v>
+        <v>25.3</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>244.1</v>
+        <v>26.9</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>24.1</v>
+        <v>4.1</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>26.8</v>
+        <v>2.2</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>79.8</v>
-      </c>
-      <c r="Z25" s="3" t="n">
-        <v>7.3</v>
-      </c>
+        <v>22.2</v>
+      </c>
+      <c r="Z25" s="3" t="n"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2597,7 +2638,7 @@
         <v>90</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>25.1</v>
+        <v>26.3</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>21</v>
@@ -2606,65 +2647,63 @@
         <v>23.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>14.1</v>
+        <v>4.1</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.2</v>
+        <v>6.7</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>24.4</v>
+        <v>2.4</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>924</v>
+        <v>21.4</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>26.8</v>
+        <v>25.5</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>1297</v>
+        <v>93</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>24.3</v>
+        <v>21.3</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>28</v>
+        <v>28.7</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>92</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>23.8</v>
+        <v>4.4</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>27.1</v>
+        <v>26.8</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="Z26" s="3" t="n">
-        <v>3.8</v>
-      </c>
+        <v>87.2</v>
+      </c>
+      <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2682,74 +2721,76 @@
         <v>322</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>30.5</v>
+        <v>25.1</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>20.6</v>
+        <v>26.6</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>9.9</v>
+        <v>39.9</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+34
+</t>
+        </is>
       </c>
       <c r="K27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>24.4</v>
+        <v>20.2</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="N27" s="8" t="n">
-        <v>22.8</v>
+      <c r="N27" s="3" t="n">
+        <v>24</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>100</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>24.9</v>
+        <v>4.9</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>73.2</v>
+        <v>92</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>10.5</v>
+        <v>1.5</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>29</v>
+        <v>27.1</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="Z27" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z27" s="3" t="n"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2764,10 +2805,10 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2990.7</v>
+        <v>290.7</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>31.8</v>
+        <v>20.5</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>20.5</v>
@@ -2775,7 +2816,7 @@
       <c r="F28" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="G28" s="8" t="n">
+      <c r="G28" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H28" s="3" t="n">
@@ -2788,22 +2829,22 @@
         <v>3.8</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L28" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>4.9</v>
+        <v>98</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>31.2</v>
@@ -2812,28 +2853,28 @@
         <v>24.8</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>27.2</v>
+        <v>2.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>60.2</v>
+        <v>33.2</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>28.6</v>
+        <v>26.3</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>24.4</v>
+        <v>3.4</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>28.4</v>
+        <v>9</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>81.8</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>6.4</v>
+        <v>1.7</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2849,22 +2890,22 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3468.1</v>
+        <v>86.5</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>31.5</v>
+        <v>36.8</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>20.5</v>
+        <v>2.5</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="H29" s="8" t="n">
-        <v>18.9</v>
+        <v>1</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>2.2</v>
@@ -2876,49 +2917,49 @@
         <v>8.4</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>28.1</v>
+        <v>21.1</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>20.6</v>
+        <v>50.6</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>24.1</v>
+        <v>22.9</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>195.3</v>
+        <v>27.3</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="Q29" s="8" t="n">
-        <v>25.3</v>
+      <c r="Q29" s="3" t="n">
+        <v>85.3</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>23.6</v>
+        <v>2.6</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>28</v>
+        <v>27.2</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>27</v>
+        <v>6.2</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>14.2</v>
+        <v>24.2</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>22.4</v>
+        <v>28.6</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>24.6</v>
+        <v>4.6</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>36.1</v>
+        <v>2.4</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2934,76 +2975,76 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1056.2</v>
+        <v>56.6</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>145.2</v>
+        <v>31.5</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>3.2</v>
+        <v>13.2</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>124.2</v>
+        <v>26.2</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>42</v>
+        <v>428</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>119.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>38.8</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>106.5</v>
+        <v>16.5</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1159.2</v>
+        <v>152.6</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>23.9</v>
+        <v>123.9</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>487.6</v>
+        <v>95.3</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>1185.8</v>
+        <v>35.8</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>120.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>140.9</v>
+        <v>28</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>396.8</v>
+        <v>22</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>14.2</v>
+        <v>9.5</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>126.1</v>
+        <v>22.4</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>135.8</v>
+        <v>24.6</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>90.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>2.5</v>
+        <v>25.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3022,28 +3063,28 @@
         <v>211.2</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>29</v>
+        <v>45.2</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>24.8</v>
+        <v>4.8</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>8.4</v>
+        <v>28.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>96.59999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>7.1</v>
+        <v>2.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>38.8</v>
+        <v>0.9</v>
+      </c>
+      <c r="K31" s="8" t="n">
+        <v>1117.1</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>21.3</v>
@@ -3051,44 +3092,44 @@
       <c r="M31" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="N31" s="8" t="n">
-        <v>23.9</v>
+      <c r="N31" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>97.5</v>
+        <v>482.6</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>27.2</v>
+        <v>97.2</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="S31" s="3" t="n">
+      <c r="S31" s="8" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>396.8</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="X31" s="8" t="n">
         <v>28.2</v>
       </c>
-      <c r="T31" s="3" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="W31" s="8" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>27.2</v>
-      </c>
       <c r="Y31" s="3" t="n">
-        <v>4.2</v>
+        <v>441.7</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3107,73 +3148,73 @@
         <v>384.7</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>31.1</v>
+        <v>29</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>952.1</v>
+        <v>25.6</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>19.3</v>
+        <v>18</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J32" s="8" t="n">
-        <v>14.6</v>
+        <v>0.4</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="8" t="n">
+      <c r="L32" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="N32" s="8" t="n">
-        <v>24.8</v>
+        <v>26.1</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>100</v>
+        <v>78.5</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="R32" s="8" t="n">
-        <v>24.9</v>
+        <v>34.1</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43.9</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>22.5</v>
+        <v>28.2</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>61</v>
+        <v>9.4</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>25.2</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>27.2</v>
+        <v>92.2</v>
       </c>
       <c r="Y32" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>5.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3189,76 +3230,79 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>213.3</v>
+        <v>242.3</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>29.2</v>
+        <v>31.1</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>24.4</v>
+        <v>244.4</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="H33" s="8" t="n">
-        <v>18</v>
+      <c r="H33" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>51.6</v>
+        <v>1.6</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>14.8</v>
+        <v>4.9</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="M33" s="8" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>23.5</v>
+      <c r="M33" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>99</v>
+        <v>160</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="R33" s="8" t="n">
-        <v>84.59999999999999</v>
+        <v>2.9</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>982.1</v>
+        <v>7.5</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>61</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>25.6</v>
+        <v>2.4</v>
       </c>
       <c r="W33" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X33" s="3" t="n">
-        <v>28.3</v>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2862 2
+</t>
+        </is>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3277,28 +3321,32 @@
         <v>311.6</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F34" s="8" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+214
+</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>18.8</v>
+        <v>20.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>1</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>21.8</v>
@@ -3306,44 +3354,44 @@
       <c r="M34" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="N34" s="8" t="n">
-        <v>25.4</v>
+      <c r="N34" s="3" t="n">
+        <v>85.90000000000001</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>1199</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>20.5</v>
+        <v>30.5</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>30.2</v>
+        <v>28.2</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>20.9</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="W34" s="8" t="n">
-        <v>138248.4</v>
+        <v>25.6</v>
+      </c>
+      <c r="W34" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>29.7</v>
+        <v>22.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>262.1</v>
+        <v>4.6</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3362,7 +3410,7 @@
         <v>353.4</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>31.1</v>
+        <v>31.9</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>20.8</v>
@@ -3374,16 +3422,16 @@
         <v>10.3</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>20.2</v>
+        <v>19.7</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>12.4</v>
+        <v>2</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>21.6</v>
@@ -3392,43 +3440,43 @@
         <v>21.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>25.9</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>97.8</v>
+        <v>92</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q35" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q35" s="3" t="n">
         <v>31.1</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>26.9</v>
+        <v>0.2</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>27.5</v>
+        <v>30.2</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>61.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>17.4</v>
+        <v>7.4</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="W35" s="8" t="n">
-        <v>46.6</v>
+        <v>72.3</v>
+      </c>
+      <c r="W35" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>28.9</v>
+        <v>8.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>82</v>
+        <v>4.4</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>6.5</v>
+        <v>0.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3447,7 +3495,7 @@
         <v>430.7</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>32.1</v>
+        <v>31.1</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>20.9</v>
@@ -3456,34 +3504,34 @@
         <v>26.5</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>19.8</v>
+        <v>12.8</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>14.4</v>
+        <v>4.4</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="L36" s="8" t="n">
-        <v>41</v>
+      <c r="L36" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>25.1</v>
+        <v>4.2</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>972.5</v>
+        <v>97.5</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>10.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>32.1</v>
@@ -3492,28 +3540,28 @@
         <v>26</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>29.7</v>
+        <v>7.5</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>62.2</v>
       </c>
-      <c r="U36" s="3" t="n">
-        <v>18</v>
+      <c r="U36" s="8" t="n">
+        <v>82</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="W36" s="8" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="W36" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>28.3</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>79.40000000000001</v>
+        <v>28.3</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>8.4</v>
+        <v>0.1</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3529,16 +3577,16 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1693.7</v>
+        <v>693.7</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>155.4</v>
+        <v>32.1</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>102</v>
+        <v>12</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1887.1</v>
+        <v>128.7</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>53.4</v>
@@ -3547,58 +3595,66 @@
         <v>96.5</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>10.1</v>
+        <v>4</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.4</v>
+        <v>18.1</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>35.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>1015.9</v>
+        <v>15.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1192.7</v>
+        <v>42.7</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>153.7</v>
+        <v>53.7</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>126.2</v>
       </c>
-      <c r="S37" s="3" t="n">
-        <v>1143.1</v>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">792798
+11811
+</t>
+        </is>
       </c>
       <c r="T37" s="3" t="n">
         <v>324.8</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>77.7</v>
+        <v>3.7</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>136.8</v>
+        <v>28.7</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>121.6</v>
+        <v>46.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>7.2</v>
+        <v>12.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="Z37" s="3" t="n">
-        <v>1.1</v>
+        <v>726</v>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82745857727
+12119
+</t>
+        </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3617,73 +3673,73 @@
         <v>338.7</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>31</v>
+        <v>5.4</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>20.4</v>
+        <v>0.2</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>25.7</v>
+        <v>25.2</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>19.3</v>
+        <v>2.3</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>18.1</v>
+        <v>3.6</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>35.6</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="N38" s="8" t="n">
-        <v>28.1</v>
+        <v>41.2</v>
+      </c>
+      <c r="M38" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>4.8</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>98.5</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q38" s="3" t="n">
-        <v>20.7</v>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Q38" s="8" t="n">
+        <v>60.7</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="S38" s="3" t="n">
-        <v>28.6</v>
+      <c r="S38" s="8" t="n">
+        <v>43.1</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="V38" s="3" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="X38" s="3" t="n">
-        <v>28.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="W38" s="8" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="X38" s="8" t="n">
+        <v>92.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>98.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>1.9</v>
+        <v>39.7</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3699,76 +3755,80 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332.5</v>
+        <v>32.5</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>31.9</v>
+        <v>31</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>20.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H39" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H39" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0.6</v>
+        <v>8.9</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="N39" s="8" t="n">
-        <v>14.8</v>
+        <v>84</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+111
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>20.6</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>31.9</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>89.8</v>
+        <v>28.6</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>63.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>17.3</v>
+        <v>12.3</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>24.7</v>
+        <v>28.4</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>23.2</v>
+        <v>24.3</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>27.6</v>
+        <v>28.5</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>38.6</v>
+        <v>2.9</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3783,11 +3843,15 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
-        <v>453.7</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>32.9</v>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7924
+265
+</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>19.2</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>18.8</v>
@@ -3796,16 +3860,16 @@
         <v>25.9</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H40" s="8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H40" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>12.7</v>
+        <v>2.7</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
@@ -3813,17 +3877,21 @@
       <c r="L40" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M40" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="N40" s="8" t="n">
-        <v>46.8</v>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+111
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>97.8</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>32.8</v>
@@ -3831,29 +3899,29 @@
       <c r="R40" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="S40" s="8" t="n">
-        <v>29.3</v>
+      <c r="S40" s="3" t="n">
+        <v>22.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>59.2</v>
+        <v>2.6</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>20.2</v>
+        <v>2.6</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>27.8</v>
+        <v>24.2</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>23.8</v>
+        <v>2.2</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>26.9</v>
+        <v>2.5</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>98.2</v>
+        <v>7.1</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>10.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3868,41 +3936,45 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n">
-        <v>265.6</v>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7924
+265
+</t>
+        </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>31.6</v>
+        <v>32.9</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="F41" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H41" s="8" t="n">
-        <v>18</v>
+      <c r="H41" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>43.4</v>
+        <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>19.9</v>
+        <v>9.9</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="N41" s="8" t="n">
-        <v>28.6</v>
+      <c r="N41" s="3" t="n">
+        <v>23</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>99</v>
@@ -3917,28 +3989,28 @@
         <v>21.4</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>24.9</v>
+        <v>29.3</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>92.3</v>
+        <v>22.3</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="V41" s="8" t="n">
-        <v>28.1</v>
+      <c r="V41" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>23.4</v>
+        <v>23.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>28</v>
+        <v>2.5</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>22</v>
+        <v>29.6</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>8.9</v>
+        <v>1.4</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3956,7 +4028,7 @@
       <c r="C42" s="3" t="n">
         <v>236.3</v>
       </c>
-      <c r="D42" s="8" t="n">
+      <c r="D42" s="3" t="n">
         <v>31.6</v>
       </c>
       <c r="E42" s="3" t="n">
@@ -3966,34 +4038,34 @@
         <v>25.9</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>20</v>
+        <v>1.3</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>26</v>
       </c>
       <c r="I42" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K42" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="J42" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>28.7</v>
-      </c>
       <c r="L42" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="M42" s="8" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="M42" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="Q42" s="3" t="n">
         <v>24.1</v>
@@ -4002,28 +4074,28 @@
         <v>23.8</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>89.3</v>
+        <v>24.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>97.7</v>
+        <v>92.2</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>24.6</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>28.2</v>
+        <v>2.7</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>29.6</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4039,40 +4111,40 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>372.2</v>
+        <v>72.2</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>30</v>
+        <v>31.6</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>85.7</v>
+        <v>5.7</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="H43" s="8" t="n">
+      <c r="H43" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>21.5</v>
+        <v>24.5</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>95.59999999999999</v>
+        <v>354.6</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>99</v>
@@ -4084,31 +4156,31 @@
         <v>29.1</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>25.5</v>
+        <v>23.8</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>30.4</v>
+        <v>29.3</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>75.59999999999999</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>84.7</v>
+        <v>2.7</v>
+      </c>
+      <c r="W43" s="8" t="n">
+        <v>23.5</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>9.1</v>
+        <v>2.1</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>78</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4127,7 +4199,7 @@
         <v>365.9</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>32.6</v>
+        <v>30</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>21.3</v>
@@ -4136,7 +4208,7 @@
         <v>26.9</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>11.3</v>
+        <v>1.3</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>19.4</v>
@@ -4151,49 +4223,49 @@
         <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>22.3</v>
+        <v>28.3</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>82.3</v>
+        <v>2.3</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>22.6</v>
+        <v>32.6</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>26.4</v>
+        <v>66.8</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>30.4</v>
+        <v>24.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>62</v>
+        <v>62.1</v>
       </c>
       <c r="U44" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>88.5</v>
+        <v>46.2</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>26.3</v>
+        <v>24.7</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>22.8</v>
+        <v>32.8</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4209,77 +4281,71 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>20.8</v>
+        <v>2.2</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>1901.6</v>
+        <v>32.6</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>121.6</v>
+        <v>2.1</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>156.1</v>
+        <v>56.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>427.4</v>
+        <v>14.7</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>18.8</v>
+        <v>28.9</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0</v>
+        <v>728.3</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>22.3</v>
+        <v>726.3</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>1825.9</v>
+        <v>3.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>26.9</v>
+        <v>98.7</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>5983.8</v>
+        <v>93.8</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>172.8</v>
-      </c>
-      <c r="R45" s="3" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>0.7</v>
-      </c>
+        <v>22.8</v>
+      </c>
+      <c r="R45" s="3" t="n"/>
+      <c r="S45" s="3" t="n"/>
       <c r="T45" s="3" t="n">
-        <v>5</v>
+        <v>450</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>25.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>5.8</v>
+        <v>358.1</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>144.9</v>
+        <v>26.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>77.5</v>
+        <v>172.5</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>503.7</v>
-      </c>
-      <c r="Z45" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>6.2</v>
+      </c>
+      <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4294,19 +4360,19 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>237.6</v>
+        <v>37.6</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>31.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>20.2</v>
+        <v>2.2</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>19.1</v>
@@ -4317,52 +4383,52 @@
       <c r="J46" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K46" s="3" t="n"/>
+      <c r="K46" s="8" t="n">
+        <v>28.3</v>
+      </c>
       <c r="L46" s="3" t="n">
-        <v>21.1</v>
+        <v>41.1</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>84.8</v>
+        <v>24.8</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>21.8</v>
+        <v>4.8</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>29</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>26.3</v>
+        <v>6.3</v>
       </c>
       <c r="W46" s="8" t="n">
-        <v>14.1</v>
+        <v>44.2</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="Z46" s="3" t="n">
-        <v>5.7</v>
-      </c>
+        <v>23.7</v>
+      </c>
+      <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,75 +736,75 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>29.2</v>
+        <v>186.2</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>29.7</v>
+        <v>28.1</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>24.3</v>
+        <v>843.1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>1.2</v>
+        <v>18.7</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>118.2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>22.9</v>
+        <v>12.9</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="8" t="n">
         <v>20.2</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>2.4</v>
+      <c r="N4" s="8" t="n">
+        <v>83.40000000000001</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>99.09999999999999</v>
+        <v>199</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
+        <v>10.2</v>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
       <c r="R4" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="S4" s="3" t="n">
+      <c r="S4" s="8" t="n">
         <v>27.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>683.9</v>
-      </c>
-      <c r="U4" s="3" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="U4" s="8" t="n">
         <v>12.2</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X4" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X4" s="8" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="Z4" s="3" t="n"/>
+        <v>1811.8</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>15.8</v>
+      </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -819,19 +819,23 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="D5" s="3" t="n">
+        <v>2903.8</v>
+      </c>
+      <c r="D5" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="E5" s="3" t="n"/>
+      <c r="E5" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="F5" s="3" t="n">
-        <v>5.1</v>
+        <v>25.4</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H5" s="3" t="n"/>
+        <v>34.1</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="I5" s="3" t="n">
         <v>3.5</v>
       </c>
@@ -839,51 +843,53 @@
         <v>5.5</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>82.90000000000001</v>
+        <v>18.9</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N5" s="3" t="n">
-        <v>26.6</v>
+      <c r="N5" s="8" t="n">
+        <v>21.6</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>292</v>
+        <v>199</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q5" s="8" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>2.5</v>
+        <v>10.2</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="R5" s="8" t="n">
+        <v>25.4</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>56.6</v>
+        <v>156.6</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>2</v>
+        <v>21.2</v>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="W5" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="X5" s="8" t="n">
+        <v>27.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="Z5" s="3" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>8.6</v>
+      </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -898,17 +904,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-13
-</t>
-        </is>
+        <v>1422.3</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>26.5</v>
@@ -916,17 +918,17 @@
       <c r="G6" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>7.7</v>
+      <c r="H6" s="8" t="n">
+        <v>872.6</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J6" s="8" t="n">
-        <v>22.6</v>
+        <v>14.6</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>7.2</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>20</v>
@@ -938,40 +940,40 @@
         <v>23.3</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>32.7</v>
+        <v>10</v>
+      </c>
+      <c r="Q6" s="8" t="n">
+        <v>21.7</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="S6" s="3" t="n">
-        <v>22.6</v>
+      <c r="S6" s="8" t="n">
+        <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>21.2</v>
+        <v>2929.8</v>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v>20.7</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>2.8</v>
+        <v>28.2</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>6.4</v>
+        <v>26.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>22.2</v>
+        <v>166.4</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -986,73 +988,75 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">486860108728
-171171808
-</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n"/>
+      <c r="C7" s="3" t="n">
+        <v>4785.1</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>34.1</v>
+      </c>
       <c r="E7" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>22</v>
+        <v>19.3</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>27</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>5.4</v>
+        <v>15.4</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>3.2</v>
+        <v>7.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="M7" s="3" t="n"/>
+        <v>20.1</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>20.1</v>
+      </c>
       <c r="N7" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="R7" s="8" t="n">
         <v>22.5</v>
       </c>
-      <c r="O7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>22.1</v>
+      <c r="S7" s="8" t="n">
+        <v>27.1</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>24.9</v>
+        <v>120.6</v>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v>29.5</v>
       </c>
       <c r="W7" s="8" t="n">
-        <v>26.1</v>
+        <v>24.4</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="Y7" s="3" t="n"/>
+        <v>27.3</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>166.2</v>
+      </c>
       <c r="Z7" s="3" t="n">
         <v>13.8</v>
       </c>
@@ -1070,73 +1074,73 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>292.6</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>1299</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>20.6</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>27.6</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="I8" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="I8" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="J8" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>36.9</v>
+        <v>14</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>30.9</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="M8" s="3" t="n">
-        <v>26.6</v>
+      <c r="M8" s="8" t="n">
+        <v>20.6</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>24</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>96.5</v>
+        <v>196.5</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>24.4</v>
+        <v>10.8</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>21.4</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>2.2</v>
+        <v>21.2</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>25.1</v>
+        <v>23.1</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>98</v>
+        <v>298</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>6.5</v>
+        <v>10.4</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>4.9</v>
+        <v>22.2</v>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>1.9</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>2.3</v>
+        <v>26.1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>7.4</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>20.6</v>
@@ -1155,74 +1159,76 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>783.5</v>
+        <v>11783.5</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>161.8</v>
+        <v>164.8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>962.9</v>
+        <v>196.9</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>130.8</v>
+        <v>1130.8</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>161.9</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>278.5</v>
+        <v>127.5</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>30.9</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>10.2</v>
+        <v>100.2</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>9292.6</v>
+        <v>199.6</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>18.8</v>
+        <v>112.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>94.5</v>
+        <v>1494.5</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>49.6</v>
+        <v>149.6</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>121.2</v>
+        <v>121.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>135.7</v>
+        <v>1135.7</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>2292.9</v>
+        <v>329.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>6.4</v>
+        <v>96</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>132.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>133.5</v>
+        <v>1116.8</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="Y9" s="3" t="n"/>
+        <v>1133.5</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>1388.8</v>
+      </c>
       <c r="Z9" s="3" t="n">
-        <v>6.6</v>
+        <v>141.6</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1238,25 +1244,22 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>33.9</v>
+        <v>356.7</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>393</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.4</v>
+        <v>19.4</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 36
-</t>
-        </is>
+      <c r="G10" s="8" t="n">
+        <v>13.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>7.9</v>
+        <v>17.9</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>3.3</v>
@@ -1264,53 +1267,51 @@
       <c r="J10" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K10" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="L10" s="3" t="n">
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="8" t="n">
         <v>20</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>9.9</v>
+        <v>19.9</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>23.2</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>22.9</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="R10" s="3" t="n">
+      <c r="Q10" s="8" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="R10" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>2.1</v>
+        <v>27.1</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="W10" s="3" t="n">
+        <v>166</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="W10" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="X10" s="8" t="n">
-        <v>88.8</v>
+      <c r="X10" s="3" t="n">
+        <v>26.7</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>7.8</v>
+        <v>79.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>4.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1326,74 +1327,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>265.6</v>
+        <v>1265.6</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>60.1</v>
+        <v>30.1</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2.8</v>
+        <v>19.8</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>245.9</v>
+        <v>24.9</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="M11" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="M11" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="N11" s="3" t="n">
-        <v>4.5</v>
+      <c r="N11" s="8" t="n">
+        <v>24.5</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>23.3</v>
+        <v>927.3</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>994.9</v>
+        <v>29.9</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>5.5</v>
+        <v>25.5</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>66</v>
+        <v>170.6</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v>26.6</v>
+        <v>12.4</v>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v>27.1</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>2.7</v>
+        <v>24.9</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>340.3</v>
-      </c>
-      <c r="Y11" s="3" t="n"/>
+        <v>30.1</v>
+      </c>
+      <c r="Y11" s="3" t="n">
+        <v>684</v>
+      </c>
       <c r="Z11" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1409,84 +1412,76 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E12" s="3" t="n">
+        <v>247.1</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="E12" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-191
-</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H12" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2.7</v>
+        <v>22.1</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>4.6</v>
+        <v>14.6</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L12" s="8" t="n">
         <v>23.3</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="8" t="n">
         <v>23</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>97.90000000000001</v>
+        <v>21.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
-711
-</t>
-        </is>
+        <v>27.5</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>31.8</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>4.9</v>
+        <v>24.9</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>20.6</v>
+        <v>59.8</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>3.8</v>
+        <v>19.8</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="W12" s="3" t="n">
-        <v>24.9</v>
+        <v>27.9</v>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>284.6</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>3.1</v>
+        <v>28.8</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>2292.7</v>
+        <v>76.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>57.2</v>
+        <v>181.7</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1502,34 +1497,34 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>122.6</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>1.2</v>
+        <v>1428.6</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>32.8</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F13" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F13" s="8" t="n">
         <v>26.6</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>1.9</v>
+        <v>19.9</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>3.3</v>
+        <v>13.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>2.1</v>
+        <v>22.1</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>21.9</v>
@@ -1538,40 +1533,40 @@
         <v>26.1</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R13" s="3" t="n">
-        <v>4.6</v>
+      <c r="R13" s="8" t="n">
+        <v>24.6</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>7.8</v>
+        <v>52.7</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="V13" s="3" t="n">
-        <v>7.9</v>
+        <v>23.3</v>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X13" s="8" t="n">
-        <v>72.7</v>
+        <v>24.8</v>
+      </c>
+      <c r="X13" s="3" t="n">
+        <v>29.3</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>7.6</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>0.2</v>
+        <v>18.3</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1587,13 +1582,13 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>90.3</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>12.9</v>
+        <v>190.3</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>26.3</v>
@@ -1601,8 +1596,8 @@
       <c r="G14" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="H14" s="3" t="n">
-        <v>26.3</v>
+      <c r="H14" s="8" t="n">
+        <v>20.3</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>1.5</v>
@@ -1610,23 +1605,23 @@
       <c r="J14" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K14" s="3" t="n">
-        <v>1.1</v>
+      <c r="K14" s="8" t="n">
+        <v>11.1</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.2</v>
+        <v>22.4</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>22.1</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>26.4</v>
+        <v>264</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>97.3</v>
+        <v>197.3</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>22.4</v>
@@ -1634,27 +1629,29 @@
       <c r="R14" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="S14" s="3" t="n">
-        <v>4.2</v>
+      <c r="S14" s="8" t="n">
+        <v>24.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>52.7</v>
+        <v>189</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="W14" s="3" t="n"/>
-      <c r="X14" s="3" t="n">
-        <v>834.3</v>
+        <v>22</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="X14" s="8" t="n">
+        <v>25.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>96</v>
+        <v>196</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1670,34 +1667,34 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>35.6</v>
+        <v>359.6</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>32.5</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F15" s="3" t="n">
+      <c r="E15" s="8" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F15" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>1.7</v>
+      <c r="G15" s="8" t="n">
+        <v>11.7</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>2.4</v>
+        <v>18.4</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.9</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>4.6</v>
+        <v>21.6</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>21.6</v>
@@ -1706,12 +1703,12 @@
         <v>25.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1006</v>
+        <v>1100</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="8" t="n">
         <v>32</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1721,25 +1718,25 @@
         <v>29.2</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>82</v>
+        <v>161.7</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="W15" s="3" t="n">
-        <v>26.8</v>
+        <v>28.7</v>
+      </c>
+      <c r="W15" s="8" t="n">
+        <v>24.8</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>25.5</v>
+        <v>28.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>3.1</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0.9</v>
+        <v>10.1</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1755,25 +1752,25 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1599.2</v>
+        <v>1291.2</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>152.9</v>
+        <v>157.9</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>15.5</v>
+        <v>1105.5</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>131.7</v>
+        <v>5131.7</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>52.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>392.2</v>
+        <v>99.2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.5</v>
+        <v>111.5</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>19.4</v>
@@ -1782,49 +1779,49 @@
         <v>36.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>10.6</v>
+        <v>1110.6</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>19.5</v>
+        <v>109.5</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>130.7</v>
+        <v>1130.7</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>20.1</v>
+        <v>27490.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>48.2</v>
+        <v>148.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>121.9</v>
+        <v>1121.9</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>36.1</v>
+        <v>1136.1</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>61.7</v>
+        <v>331.8</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>26.6</v>
+        <v>176.6</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>28.7</v>
+        <v>133.7</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>120.7</v>
+        <v>1120.7</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>28.8</v>
+        <v>162.5</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>47.6</v>
+        <v>1407.4</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1.6</v>
+        <v>34.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1840,76 +1837,74 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>3418.2</v>
+        <v>1318.2</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>31.6</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>24.1</v>
+        <v>21.1</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>26.3</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>2.3</v>
+        <v>12.3</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K17" s="3" t="n">
-        <v>36.8</v>
-      </c>
+      <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="8" t="n">
         <v>21.9</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>2.7</v>
+        <v>29.7</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>4.4</v>
+        <v>24.4</v>
       </c>
       <c r="S17" s="8" t="n">
-        <v>36.4</v>
+        <v>28.2</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>331.8</v>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="W17" s="3" t="n">
+        <v>166.4</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="W17" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="X17" s="8" t="n">
-        <v>42.5</v>
+      <c r="X17" s="3" t="n">
+        <v>28.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>81.5</v>
+        <v>181.5</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>34.4</v>
+        <v>16.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1925,40 +1920,40 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>368.6</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>32.1</v>
+        <v>1368</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>82.09999999999999</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>26.7</v>
+        <v>24.2</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>286.1</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>6.4</v>
+        <v>10.9</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J18" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>7.6</v>
+      <c r="J18" s="8" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>10.4</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>22.1</v>
+        <v>21.4</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="N18" s="3" t="n">
-        <v>4.8</v>
+      <c r="N18" s="8" t="n">
+        <v>224.8</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>97.3</v>
@@ -1969,32 +1964,32 @@
       <c r="Q18" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="S18" s="3" t="n">
-        <v>0.3</v>
+      <c r="S18" s="8" t="n">
+        <v>27.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="V18" s="3" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="W18" s="3" t="n">
-        <v>24.1</v>
+      <c r="V18" s="8" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="W18" s="8" t="n">
+        <v>24.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>28.5</v>
+        <v>21.9</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>119</v>
+        <v>71.2</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>6.9</v>
+        <v>111</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2010,80 +2005,76 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>2260.6</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>30.4</v>
+        <v>308.4</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F19" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="F19" s="8" t="n">
         <v>26.3</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H19" s="3" t="n">
-        <v>2.4</v>
+      <c r="H19" s="8" t="n">
+        <v>21.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>2.3</v>
+        <v>11.2</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>22.3</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">662
-1254
-</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>86.3</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>197.6</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q19" s="8" t="n">
-        <v>92.90000000000001</v>
+        <v>10.6</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>29.9</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>26</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>7.7</v>
+        <v>31.1</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>58</v>
+        <v>73.7</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>8.5</v>
+        <v>11</v>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v>24.3</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="X19" s="3" t="n">
-        <v>29</v>
+        <v>22.9</v>
+      </c>
+      <c r="X19" s="8" t="n">
+        <v>71.09999999999999</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>2.2</v>
+        <v>89</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>1</v>
+        <v>78.3</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2104,75 +2095,71 @@
       <c r="D20" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="E20" s="8" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>24.5</v>
+      <c r="E20" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>26.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>29.9</v>
+        <v>19.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="I20" s="3" t="n">
-        <v>2.5</v>
+      <c r="I20" s="8" t="n">
+        <v>28.1</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">662
-1254
-</t>
-        </is>
+        <v>21.4</v>
+      </c>
+      <c r="N20" s="8" t="n">
+        <v>35.4</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>30.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v>21.8</v>
+        <v>30.1</v>
+      </c>
+      <c r="R20" s="8" t="n">
+        <v>24.8</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>31.1</v>
+        <v>27.5</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>3.2</v>
+        <v>162.3</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>2.9</v>
+        <v>27.3</v>
+      </c>
+      <c r="W20" s="8" t="n">
+        <v>23.8</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>2.3</v>
+        <v>27.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>9.1</v>
+        <v>715</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>3.3</v>
+        <v>19.1</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2194,13 +2181,13 @@
         <v>30.7</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>22.2</v>
+        <v>21.2</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>24.5</v>
+        <v>25.9</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>9.5</v>
+        <v>29.5</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>19.6</v>
@@ -2212,22 +2199,22 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>21.6</v>
+        <v>10</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>18.6</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>2.6</v>
+        <v>25.6</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>92</v>
+        <v>199</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>30.6</v>
@@ -2236,27 +2223,29 @@
         <v>26.2</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>27.5</v>
+        <v>31.2</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>6.3</v>
+        <v>71.2</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V21" s="3" t="n">
-        <v>7.3</v>
+      <c r="V21" s="8" t="n">
+        <v>78.8</v>
       </c>
       <c r="W21" s="8" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="X21" s="8" t="n">
-        <v>25</v>
+        <v>16.6</v>
+      </c>
+      <c r="X21" s="3" t="n">
+        <v>28.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="Z21" s="3" t="n"/>
+        <v>77.3</v>
+      </c>
+      <c r="Z21" s="3" t="n">
+        <v>18.4</v>
+      </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -2273,41 +2262,41 @@
       <c r="C22" s="3" t="n">
         <v>399.3</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="8" t="n">
         <v>32.9</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>22</v>
+      <c r="F22" s="8" t="n">
+        <v>27</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1.8</v>
+        <v>12.8</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>12.8</v>
+        <v>19.8</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2.5</v>
+        <v>12.5</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>4.3</v>
+        <v>14.3</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>2.4</v>
+        <v>21</v>
+      </c>
+      <c r="N22" s="8" t="n">
+        <v>24.7</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>7.5</v>
+        <v>97.5</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.4</v>
@@ -2319,27 +2308,29 @@
         <v>25.9</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>31.2</v>
+        <v>89.3</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>212.6</v>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v>92.2</v>
+        <v>160.5</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>4.1</v>
+        <v>26.8</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="X22" s="3" t="n">
-        <v>8.9</v>
+        <v>24.6</v>
+      </c>
+      <c r="X22" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="Z22" s="3" t="n"/>
+        <v>186</v>
+      </c>
+      <c r="Z22" s="3" t="n">
+        <v>14.9</v>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -2354,14 +2345,10 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>732.6</v>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422999227
-1149 6
-</t>
-        </is>
+        <v>17439.6</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>164.5</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>107.2</v>
@@ -2370,14 +2357,10 @@
         <v>132.4</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4574532851
-12818
-</t>
-        </is>
+        <v>250.3</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>1101.8</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>10.9</v>
@@ -2386,56 +2369,52 @@
         <v>19.3</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>19.3</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>18.2</v>
+        <v>108.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>107</v>
+        <v>1107</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>126.8</v>
+        <v>1126.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>48.9</v>
+        <v>1489.4</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>55.7</v>
+        <v>155.7</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>128.1</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>89.3</v>
+        <v>1146.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>6.5</v>
+        <v>325.1</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>2.4</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>6.5</v>
+        <v>134.4</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>24.6</v>
+        <v>120.3</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>29.7</v>
+        <v>140.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="Z23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-78
-</t>
-        </is>
+        <v>2399</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>36.7</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2451,43 +2430,41 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>4.2</v>
+        <v>347.9</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>57.5</v>
+        <v>315.1</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>26.3</v>
+        <v>26.5</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>1.8</v>
+        <v>10.1</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>12.2</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>5.4</v>
+        <v>21.4</v>
+      </c>
+      <c r="N24" s="8" t="n">
+        <v>22.4</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>27.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>0.4</v>
@@ -2499,32 +2476,28 @@
         <v>25.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>46.8</v>
+        <v>29.4</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>32.5</v>
+        <v>165.1</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>40.8</v>
+        <v>15.9</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="W24" s="8" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X24" s="8" t="n">
+        <v>282.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>399</v>
-      </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-78
-</t>
-        </is>
+        <v>79.8</v>
+      </c>
+      <c r="Z24" s="3" t="n">
+        <v>17.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2540,10 +2513,10 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>31.5</v>
+        <v>106.7</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>26.3</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>20.6</v>
@@ -2552,75 +2525,61 @@
         <v>23.5</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>3.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24127
-210
-</t>
-        </is>
+        <v>20.2</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>23.7</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>2.4</v>
+        <v>22.4</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>986.1</v>
+        <v>22.1</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">779717
-1791818
-</t>
-        </is>
+        <v>264.4</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>97</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0.7</v>
+        <v>10.7</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="R25" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7783
-181186
-</t>
-        </is>
+      <c r="R25" s="8" t="n">
+        <v>284.1</v>
+      </c>
+      <c r="S25" s="8" t="n">
+        <v>28.7</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>654.1</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>25.3</v>
-      </c>
+        <v>184.4</v>
+      </c>
+      <c r="U25" s="3" t="inlineStr"/>
       <c r="V25" s="3" t="n">
-        <v>26.9</v>
+        <v>244.1</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v>2.2</v>
+        <v>22.8</v>
+      </c>
+      <c r="X25" s="8" t="n">
+        <v>26.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Z25" s="3" t="n"/>
+        <v>81.7</v>
+      </c>
+      <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2635,34 +2594,34 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>90</v>
+        <v>290</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>26.3</v>
+        <v>25.1</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>23.1</v>
+      <c r="F26" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>4.1</v>
+        <v>14.1</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>20.2</v>
+        <v>19.2</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>2.5</v>
+        <v>10.9</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>6.7</v>
+        <v>16.1</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>2.4</v>
+        <v>21.4</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>21.4</v>
@@ -2671,39 +2630,41 @@
         <v>25.5</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="R26" s="3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="R26" s="8" t="n">
         <v>23.3</v>
       </c>
-      <c r="S26" s="3" t="n">
-        <v>28.7</v>
+      <c r="S26" s="8" t="n">
+        <v>280.9</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>192</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>2.3</v>
+        <v>12.9</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>4.4</v>
+        <v>23.8</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>26.8</v>
+        <v>22.8</v>
+      </c>
+      <c r="X26" s="8" t="n">
+        <v>79.09999999999999</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="Z26" s="3" t="n"/>
+        <v>191.8</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2718,38 +2679,32 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>322</v>
+        <v>2322</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>25.1</v>
+        <v>20.5</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="F27" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F27" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>39.9</v>
+        <v>19.9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-34
-</t>
-        </is>
-      </c>
+        <v>1.9</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr"/>
       <c r="K27" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>20.2</v>
+        <v>20.7</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>20.5</v>
@@ -2758,7 +2713,7 @@
         <v>24</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>100</v>
+        <v>198</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0.4</v>
@@ -2766,31 +2721,31 @@
       <c r="Q27" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R27" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="S27" s="3" t="n">
-        <v>28</v>
+      <c r="R27" s="8" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="S27" s="8" t="n">
+        <v>89</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>92</v>
+        <v>73.2</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>23.8</v>
+        <v>26.9</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>27.1</v>
+        <v>24.4</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>29</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z27" s="3" t="n"/>
+        <v>81.8</v>
+      </c>
+      <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2805,10 +2760,10 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>290.7</v>
+        <v>1290.7</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>20.5</v>
+        <v>51.8</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>20.5</v>
@@ -2816,65 +2771,63 @@
       <c r="F28" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="G28" s="8" t="n">
         <v>11.3</v>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="H28" s="3" t="inlineStr"/>
       <c r="I28" s="3" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L28" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L28" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="N28" s="3" t="n">
+      <c r="N28" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>98</v>
+        <v>297.3</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.6</v>
+        <v>10.8</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="R28" s="3" t="n">
+      <c r="R28" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="S28" s="3" t="n">
-        <v>2.9</v>
+      <c r="S28" s="8" t="n">
+        <v>27.2</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>33.2</v>
+        <v>160.2</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="V28" s="3" t="n">
-        <v>26.3</v>
+      <c r="V28" s="8" t="n">
+        <v>28.6</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>3.4</v>
+        <v>24.6</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>9</v>
+        <v>28.4</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>81.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>1.7</v>
+        <v>10.7</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2890,25 +2843,23 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>86.5</v>
+        <v>12146.8</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>36.8</v>
+        <v>31.5</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.5</v>
+        <v>20.5</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>1.5</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
       <c r="I29" s="3" t="n">
-        <v>2.2</v>
+        <v>11.6</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2.6</v>
@@ -2919,14 +2870,14 @@
       <c r="L29" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="M29" s="3" t="n">
-        <v>50.6</v>
+      <c r="M29" s="8" t="n">
+        <v>20.6</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>22.9</v>
+        <v>23.9</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>27.3</v>
+        <v>95.3</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>1.1</v>
@@ -2934,32 +2885,32 @@
       <c r="Q29" s="3" t="n">
         <v>85.3</v>
       </c>
-      <c r="R29" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>27.2</v>
+      <c r="R29" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="S29" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>6.2</v>
+        <v>87</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>24.2</v>
+        <v>14.2</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>28.6</v>
+        <v>22.4</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="X29" s="3" t="n">
-        <v>2.4</v>
+        <v>21.3</v>
+      </c>
+      <c r="X29" s="8" t="n">
+        <v>14.6</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>2.6</v>
+        <v>90.8</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>2.5</v>
+        <v>22.5</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2975,76 +2926,76 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>56.6</v>
+        <v>11056.2</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>31.5</v>
+        <v>1145.2</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>13.2</v>
+        <v>1103.2</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>26.2</v>
+        <v>124.2</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>428</v>
+        <v>142</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>96.59999999999999</v>
+        <v>196.6</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>1.6</v>
+        <v>7.1</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1</v>
+        <v>111</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>38.8</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>16.5</v>
+        <v>1106.5</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>152.6</v>
+        <v>1105.2</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>123.9</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>95.3</v>
+        <v>487.6</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>35.8</v>
+        <v>11135.8</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>120.7</v>
+        <v>120.1</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>28</v>
+        <v>1140.9</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>22</v>
+        <v>396.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>9.5</v>
+        <v>18.5</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>22.4</v>
+        <v>1126.1</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>21.3</v>
+        <v>1115.9</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>24.6</v>
+        <v>135.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>1424.7</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>25.8</v>
+        <v>21.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3063,73 +3014,71 @@
         <v>211.2</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>45.2</v>
+        <v>29</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4.8</v>
+        <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>28.4</v>
+        <v>8.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>1.3</v>
+        <v>19.3</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K31" s="8" t="n">
-        <v>1117.1</v>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="M31" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="N31" s="3" t="n">
+      <c r="M31" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="N31" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>482.6</v>
+        <v>97.5</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>97.2</v>
-      </c>
-      <c r="R31" s="3" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="R31" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="S31" s="8" t="n">
-        <v>40.9</v>
+      <c r="S31" s="3" t="n">
+        <v>28.2</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>396.8</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>38.1</v>
+        <v>79.40000000000001</v>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v>88.8</v>
       </c>
       <c r="V31" s="8" t="n">
-        <v>26.1</v>
+        <v>25.2</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="X31" s="8" t="n">
-        <v>28.2</v>
+        <v>23.2</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>27.2</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>441.7</v>
+        <v>24.9</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>5.2</v>
+        <v>145.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3148,73 +3097,69 @@
         <v>384.7</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>29</v>
+        <v>31.1</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>25.6</v>
+        <v>25.2</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H32" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H32" s="8" t="n">
         <v>18</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.4</v>
+        <v>12.3</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>4.6</v>
+        <v>14.6</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>2.2</v>
-      </c>
+        <v>20.1</v>
+      </c>
+      <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
-        <v>78.5</v>
+        <v>1100</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>43.9</v>
+        <v>31.1</v>
+      </c>
+      <c r="R32" s="8" t="n">
+        <v>24.9</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>28.2</v>
+        <v>27.5</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>17.5</v>
+        <v>161</v>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v>18.5</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>25.2</v>
+        <v>27.4</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="X32" s="3" t="n">
-        <v>92.2</v>
-      </c>
+        <v>23.8</v>
+      </c>
+      <c r="X32" s="3" t="inlineStr"/>
       <c r="Y32" s="3" t="n">
-        <v>24.9</v>
+        <v>174.6</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>19.3</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3230,79 +3175,72 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>242.3</v>
+        <v>213.3</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>31.1</v>
+        <v>29.2</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>244.4</v>
+        <v>19.6</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>24.4</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H33" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H33" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2.3</v>
+        <v>11</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L33" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L33" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>2.2</v>
-      </c>
+        <v>21.4</v>
+      </c>
+      <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>160</v>
+        <v>299</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R33" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v>7.5</v>
+        <v>28.9</v>
+      </c>
+      <c r="R33" s="8" t="n">
+        <v>206.6</v>
+      </c>
+      <c r="S33" s="8" t="n">
+        <v>28.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>61</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W33" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="W33" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2862 2
-</t>
-        </is>
-      </c>
+      <c r="X33" s="3" t="inlineStr"/>
       <c r="Y33" s="3" t="n">
-        <v>4.6</v>
+        <v>861.4</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3321,16 +3259,12 @@
         <v>311.6</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-214
-</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F34" s="8" t="n">
         <v>26.7</v>
       </c>
       <c r="G34" s="3" t="n">
@@ -3340,28 +3274,28 @@
         <v>20.2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L34" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L34" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>25.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>30.5</v>
@@ -3370,28 +3304,28 @@
         <v>25.8</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>28.2</v>
+        <v>30.2</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>20.9</v>
+        <v>169.4</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>25.6</v>
+        <v>27.3</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>23.8</v>
+        <v>24.8</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>22.8</v>
+        <v>29.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>4.6</v>
+        <v>82.8</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>6.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3410,9 +3344,9 @@
         <v>353.4</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E35" s="3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E35" s="8" t="n">
         <v>20.8</v>
       </c>
       <c r="F35" s="3" t="n">
@@ -3425,58 +3359,58 @@
         <v>19.7</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M35" s="3" t="n">
+      <c r="M35" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>25.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>92</v>
+        <v>197.2</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0.2</v>
+        <v>10.7</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="S35" s="3" t="n">
-        <v>30.2</v>
+      <c r="R35" s="8" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="S35" s="8" t="n">
+        <v>27.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>1614.3</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="W35" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="X35" s="3" t="n">
-        <v>8.9</v>
+        <v>17.4</v>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="W35" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>28.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>4.4</v>
+        <v>19.8</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>0.4</v>
+        <v>18.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3495,43 +3429,43 @@
         <v>430.7</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E36" s="3" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E36" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>26.5</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1.2</v>
+        <v>11.2</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>12.8</v>
+        <v>19.8</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K36" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="K36" s="8" t="n">
         <v>30.6</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="M36" s="3" t="n">
-        <v>20.7</v>
+      <c r="M36" s="8" t="n">
+        <v>20.1</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>4.2</v>
+        <v>26.2</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>97.5</v>
+        <v>918.5</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>32.1</v>
@@ -3540,28 +3474,28 @@
         <v>26</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>7.5</v>
+        <v>29.7</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>62.2</v>
       </c>
-      <c r="U36" s="8" t="n">
-        <v>82</v>
+      <c r="U36" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>27.8</v>
+        <v>28.7</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X36" s="3" t="n">
+      <c r="X36" s="8" t="n">
         <v>28.3</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>28.3</v>
+        <v>42.4</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.1</v>
+        <v>211</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3577,13 +3511,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>693.7</v>
+        <v>1693.7</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>32.1</v>
+        <v>1155.4</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>12</v>
+        <v>1102</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>128.7</v>
@@ -3595,66 +3529,58 @@
         <v>96.5</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>4</v>
+        <v>110.1</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>35.6</v>
+        <v>135.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>16</v>
+        <v>1106</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>15.2</v>
+        <v>1803.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>24.1</v>
+        <v>121.1</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>42.7</v>
+        <v>492.9</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>53.7</v>
+        <v>143.1</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>126.2</v>
-      </c>
-      <c r="S37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">792798
-11811
-</t>
-        </is>
+        <v>1126.2</v>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>1143.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>324.8</v>
+        <v>13821.8</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>3.7</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>28.7</v>
+        <v>136.8</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>46.6</v>
+        <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>12.4</v>
+        <v>1142.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>726</v>
-      </c>
-      <c r="Z37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82745857727
-12119
-</t>
-        </is>
+        <v>398.2</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>1392.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3673,73 +3599,71 @@
         <v>338.7</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.4</v>
+        <v>31</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0.2</v>
+        <v>20.4</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>25.2</v>
+        <v>25.7</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>2.3</v>
+        <v>19.3</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K38" s="3" t="n">
-        <v>35.6</v>
-      </c>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="M38" s="8" t="n">
-        <v>41</v>
+        <v>21.2</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>4.8</v>
+        <v>24.8</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>98.5</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Q38" s="8" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="R38" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="R38" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="S38" s="8" t="n">
-        <v>43.1</v>
+      <c r="S38" s="3" t="n">
+        <v>28.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>6</v>
+        <v>169</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>2.5</v>
+        <v>13.5</v>
       </c>
       <c r="V38" s="8" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="W38" s="8" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="X38" s="8" t="n">
-        <v>92.2</v>
+        <v>87.40000000000001</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>28.5</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>79.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>39.7</v>
+        <v>2.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3755,21 +3679,21 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>90.09999999999999</v>
-      </c>
-      <c r="F39" s="3" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F39" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H39" s="3" t="n">
+      <c r="G39" s="8" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H39" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="I39" s="3" t="n">
@@ -3778,57 +3702,51 @@
       <c r="J39" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K39" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-111
-</t>
-        </is>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>20.9</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>20.6</v>
+        <v>24.6</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>0.1</v>
+        <v>10.2</v>
       </c>
       <c r="Q39" s="3" t="n">
         <v>31.9</v>
       </c>
-      <c r="R39" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>28.6</v>
+      <c r="R39" s="8" t="n">
+        <v>126</v>
+      </c>
+      <c r="S39" s="8" t="n">
+        <v>29.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>63.2</v>
+        <v>163.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>28.4</v>
+        <v>17.3</v>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v>24.9</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>24.3</v>
+        <v>23.2</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>28.5</v>
+        <v>27.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>88.2</v>
+        <v>288.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>2.9</v>
+        <v>13.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3843,15 +3761,11 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7924
-265
-</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>19.2</v>
+      <c r="C40" s="3" t="n">
+        <v>1453.1</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>32.9</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>18.8</v>
@@ -3860,68 +3774,64 @@
         <v>25.9</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>4.1</v>
+        <v>14.1</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.7</v>
+        <v>12.7</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>5</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-111
-</t>
-        </is>
+      <c r="M40" s="8" t="n">
+        <v>19.6</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>2.6</v>
+        <v>28.6</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>97.8</v>
+        <v>1797.8</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>6.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>32.8</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" s="8" t="n">
         <v>26</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>22.8</v>
+        <v>29.3</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>2.6</v>
+        <v>39.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>2.6</v>
+        <v>20.2</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="W40" s="3" t="n">
-        <v>2.2</v>
+        <v>24.8</v>
+      </c>
+      <c r="W40" s="8" t="n">
+        <v>23.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>2.5</v>
+        <v>26.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>7.1</v>
+        <v>72</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>3.6</v>
+        <v>10.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3936,27 +3846,23 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7924
-265
-</t>
-        </is>
+      <c r="C41" s="3" t="n">
+        <v>269.6</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>32.9</v>
+        <v>31.6</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>25.6</v>
+      <c r="F41" s="8" t="n">
+        <v>85.59999999999999</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>12</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>1.2</v>
@@ -3964,11 +3870,11 @@
       <c r="J41" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="K41" s="3" t="n">
-        <v>0</v>
+      <c r="K41" s="8" t="n">
+        <v>43.6</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>9.9</v>
+        <v>19.9</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>19.8</v>
@@ -3977,10 +3883,10 @@
         <v>23</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>22.3</v>
@@ -3989,28 +3895,28 @@
         <v>21.4</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>29.3</v>
+        <v>24.9</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>22.3</v>
+        <v>192.8</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>2.5</v>
+        <v>12</v>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v>816.6</v>
+      </c>
+      <c r="W41" s="8" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="X41" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>29.6</v>
+        <v>190.5</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4026,7 +3932,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>236.3</v>
+        <v>1236.3</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>31.6</v>
@@ -4034,69 +3940,67 @@
       <c r="E42" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="F42" s="3" t="n">
+      <c r="F42" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="G42" s="3" t="n">
-        <v>1.3</v>
+      <c r="G42" s="8" t="n">
+        <v>11.3</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>1.7</v>
+        <v>10.7</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0.7</v>
+        <v>28.1</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>41.2</v>
+        <v>21.9</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="N42" s="3" t="n">
+      <c r="N42" s="8" t="n">
         <v>26</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q42" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q42" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="S42" s="3" t="n">
-        <v>24.9</v>
+      <c r="S42" s="8" t="n">
+        <v>29.3</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>92.2</v>
+        <v>197.7</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>2.7</v>
+        <v>10.1</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v>23.4</v>
+        <v>21.7</v>
+      </c>
+      <c r="W42" s="8" t="n">
+        <v>23.5</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>2.7</v>
+        <v>28.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="Z42" s="3" t="n">
-        <v>2.9</v>
-      </c>
+        <v>190.6</v>
+      </c>
+      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -4111,16 +4015,16 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>72.2</v>
+        <v>372.2</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>31.6</v>
+        <v>30</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>5.7</v>
+        <v>25.7</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>8.699999999999999</v>
@@ -4129,25 +4033,25 @@
         <v>19.8</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>2.1</v>
+        <v>12</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>24.5</v>
+        <v>21.5</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>354.6</v>
+        <v>25.6</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>0.2</v>
@@ -4156,31 +4060,31 @@
         <v>29.1</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>23.8</v>
+        <v>25.5</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>29.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="W43" s="8" t="n">
-        <v>23.5</v>
+        <v>19.8</v>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>24.7</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>2.1</v>
+        <v>29.1</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>18</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>0.5</v>
+        <v>18.2</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4199,25 +4103,25 @@
         <v>365.9</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>30</v>
+        <v>22.6</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="F44" s="3" t="n">
+      <c r="F44" s="8" t="n">
         <v>26.9</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H44" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H44" s="8" t="n">
         <v>19.4</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>3.6</v>
+        <v>19.6</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>0</v>
@@ -4226,46 +4130,46 @@
         <v>28.3</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N44" s="3" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="N44" s="8" t="n">
         <v>26.9</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>106</v>
+        <v>1100</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>32.6</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>66.8</v>
+        <v>26.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>24.8</v>
+        <v>30.1</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="U44" s="3" t="n">
+        <v>162</v>
+      </c>
+      <c r="U44" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>46.2</v>
+        <v>28.5</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>32.8</v>
+        <v>26.3</v>
+      </c>
+      <c r="X44" s="8" t="n">
+        <v>32.2</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>2.2</v>
+        <v>166</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4280,72 +4184,66 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>32.6</v>
-      </c>
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
       <c r="E45" s="3" t="n">
-        <v>2.1</v>
+        <v>1121</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>56.1</v>
+        <v>1796.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>3.7</v>
+        <v>109.1</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>14.7</v>
+        <v>114.7</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>1.2</v>
+        <v>10.7</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>28.9</v>
+        <v>18.4</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>728.3</v>
+        <v>172.3</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>726.3</v>
+        <v>1166.9</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>3.9</v>
+        <v>122.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>98.7</v>
+        <v>148.7</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>93.8</v>
+        <v>293.8</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="R45" s="3" t="n"/>
-      <c r="S45" s="3" t="n"/>
-      <c r="T45" s="3" t="n">
-        <v>450</v>
-      </c>
+        <v>1752.8</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>149.1</v>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
       <c r="U45" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>168.6</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>358.1</v>
-      </c>
-      <c r="W45" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="X45" s="3" t="n">
-        <v>172.5</v>
-      </c>
+        <v>138.1</v>
+      </c>
+      <c r="W45" s="3" t="inlineStr"/>
+      <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Z45" s="3" t="n"/>
+        <v>3503.7</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>9316</v>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4360,19 +4258,19 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>37.6</v>
+        <v>2337.6</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F46" s="3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F46" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="G46" s="3" t="n">
-        <v>1.5</v>
+      <c r="G46" s="8" t="n">
+        <v>11.5</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>19.1</v>
@@ -4381,15 +4279,13 @@
         <v>1.7</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K46" s="8" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="M46" s="3" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="M46" s="8" t="n">
         <v>20</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4399,36 +4295,38 @@
         <v>99</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>0.6</v>
+        <v>10.2</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R46" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="S46" s="3" t="n">
+      <c r="R46" s="8" t="n">
+        <v>216.8</v>
+      </c>
+      <c r="S46" s="8" t="n">
         <v>29</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>28</v>
+        <v>729</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v>6.3</v>
+        <v>11.4</v>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v>643.4</v>
       </c>
       <c r="W46" s="8" t="n">
-        <v>44.2</v>
+        <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>28.7</v>
+        <v>28.1</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="Z46" s="3" t="n"/>
+        <v>283.9</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>15.7</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>186.2</v>
+        <v>136.2</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>28.1</v>
@@ -745,65 +745,67 @@
         <v>20</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>843.1</v>
+        <v>24.5</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>118.2</v>
+        <v>81.7</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>12.9</v>
+        <v>2.9</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="8" t="n">
+      <c r="L4" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>83.40000000000001</v>
+      <c r="N4" s="3" t="n">
+        <v>23.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q4" s="3" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>28.8</v>
+      </c>
       <c r="R4" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="S4" s="8" t="n">
-        <v>27.1</v>
+      <c r="S4" s="3" t="n">
+        <v>22.1</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="U4" s="8" t="n">
+      <c r="U4" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X4" s="8" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="X4" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>1811.8</v>
+        <v>181.8</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>15.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -819,7 +821,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2903.8</v>
+        <v>203.8</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>32.6</v>
@@ -831,7 +833,7 @@
         <v>25.4</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>34.1</v>
+        <v>14.4</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>16.8</v>
@@ -843,52 +845,52 @@
         <v>5.5</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="N5" s="8" t="n">
+      <c r="N5" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>199</v>
+        <v>909</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R5" s="8" t="n">
+      <c r="R5" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>156.6</v>
+        <v>56.6</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="V5" s="8" t="n">
+      <c r="V5" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="W5" s="8" t="n">
+      <c r="W5" s="3" t="n">
         <v>24</v>
       </c>
       <c r="X5" s="8" t="n">
-        <v>27.8</v>
+        <v>72.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>11</v>
+        <v>141.1</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -904,13 +906,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1422.3</v>
-      </c>
-      <c r="D6" s="8" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>34.2</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>18.8</v>
+        <v>12.2</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>26.5</v>
@@ -919,7 +921,7 @@
         <v>15.4</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>872.6</v>
+        <v>184.6</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>14.6</v>
@@ -928,7 +930,7 @@
         <v>7.2</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>20</v>
@@ -942,38 +944,38 @@
       <c r="O6" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="P6" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q6" s="8" t="n">
-        <v>21.7</v>
+      <c r="P6" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>32.7</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="S6" s="8" t="n">
+      <c r="S6" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>2929.8</v>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v>20.7</v>
+        <v>22.8</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W6" s="3" t="n">
-        <v>23.7</v>
+      <c r="W6" s="8" t="n">
+        <v>31.7</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>166.4</v>
+        <v>16614.1</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -989,16 +991,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4785.1</v>
+        <v>6472.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>27</v>
+        <v>34.7</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>15.4</v>
@@ -1007,13 +1009,13 @@
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>4.3</v>
+        <v>47.9</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>7.9</v>
+        <v>1.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>20.1</v>
@@ -1028,37 +1030,37 @@
         <v>100</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q7" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q7" s="3" t="n">
         <v>34.2</v>
       </c>
-      <c r="R7" s="8" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="S7" s="8" t="n">
+      <c r="R7" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>120.6</v>
-      </c>
-      <c r="U7" s="8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="U7" s="3" t="n">
         <v>26.5</v>
       </c>
       <c r="V7" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="W7" s="8" t="n">
+      <c r="W7" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="X7" s="3" t="n">
         <v>27.3</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>166.2</v>
+        <v>66.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>13.8</v>
+        <v>15.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1074,12 +1076,12 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1299</v>
-      </c>
-      <c r="D8" s="8" t="n">
+        <v>299</v>
+      </c>
+      <c r="D8" s="3" t="n">
         <v>34.6</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="F8" s="3" t="n">
@@ -1089,58 +1091,58 @@
         <v>14</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K8" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="K8" s="3" t="n">
         <v>30.9</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="M8" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>24</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>196.5</v>
+        <v>96.5</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Q8" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q8" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>23.1</v>
+        <v>25.1</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>298</v>
+        <v>98</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W8" s="8" t="n">
-        <v>1.9</v>
+      <c r="W8" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>20.6</v>
@@ -1159,28 +1161,28 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>11783.5</v>
+        <v>1781.2</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>164.8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>196.9</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1130.8</v>
+        <v>1301.7</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>161.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>127.5</v>
+        <v>12.8</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>30.9</v>
@@ -1189,31 +1191,31 @@
         <v>100.2</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>199.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>112.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1494.5</v>
+        <v>894.2</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>1.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>149.6</v>
+        <v>1179.6</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>121.9</v>
+        <v>122.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1135.7</v>
+        <v>155.1</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>329.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>132.8</v>
@@ -1222,10 +1224,10 @@
         <v>1116.8</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>1133.5</v>
+        <v>133.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>1388.8</v>
+        <v>388.8</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>141.6</v>
@@ -1244,10 +1246,10 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>356.7</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>393</v>
+        <v>8188.5</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>33</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>19.4</v>
@@ -1255,20 +1257,20 @@
       <c r="F10" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="G10" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>17.9</v>
+        <v>11.9</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="8" t="n">
+      <c r="L10" s="3" t="n">
         <v>20</v>
       </c>
       <c r="M10" s="3" t="n">
@@ -1283,17 +1285,17 @@
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="8" t="n">
+      <c r="Q10" s="3" t="n">
         <v>29.9</v>
       </c>
-      <c r="R10" s="8" t="n">
-        <v>24.4</v>
+      <c r="R10" s="3" t="n">
+        <v>94.40000000000001</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>27.1</v>
+        <v>27.8</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>166</v>
+        <v>66</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>16.2</v>
@@ -1301,17 +1303,17 @@
       <c r="V10" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="W10" s="8" t="n">
+      <c r="W10" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="X10" s="3" t="n">
-        <v>26.7</v>
+      <c r="X10" s="8" t="n">
+        <v>16.2</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>79.8</v>
+        <v>72.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>18.3</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1329,7 +1331,7 @@
       <c r="C11" s="3" t="n">
         <v>1265.6</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="E11" s="3" t="n">
@@ -1345,28 +1347,28 @@
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M11" s="8" t="n">
+      <c r="M11" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="N11" s="8" t="n">
-        <v>24.5</v>
+      <c r="N11" s="3" t="n">
+        <v>24.3</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>927.3</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>10.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>29.9</v>
@@ -1374,29 +1376,29 @@
       <c r="R11" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="S11" s="3" t="n">
+      <c r="S11" s="8" t="n">
         <v>29.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>170.6</v>
+        <v>720.6</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>24.9</v>
+        <v>72.09999999999999</v>
+      </c>
+      <c r="W11" s="8" t="n">
+        <v>16.9</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>684</v>
+        <v>2894</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>5.1</v>
+        <v>11.8</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1412,13 +1414,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>247.1</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>22.6</v>
+        <v>347.1</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>82.59999999999999</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>27.2</v>
@@ -1426,32 +1428,32 @@
       <c r="G12" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="I12" s="3" t="n">
-        <v>22.1</v>
+      <c r="I12" s="8" t="n">
+        <v>227.1</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>21.9</v>
+        <v>350.5</v>
+      </c>
+      <c r="N12" s="8" t="n">
+        <v>17.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>27.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>10.8</v>
+        <v>0.5</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>31.8</v>
@@ -1460,19 +1462,19 @@
         <v>24.9</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>27.1</v>
+        <v>21.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>59.8</v>
+        <v>51.8</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="W12" s="8" t="n">
-        <v>284.6</v>
+        <v>21.9</v>
+      </c>
+      <c r="W12" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>28.8</v>
@@ -1481,7 +1483,7 @@
         <v>76.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>181.7</v>
+        <v>21.6</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1497,16 +1499,16 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1428.6</v>
-      </c>
-      <c r="D13" s="8" t="n">
+        <v>428.6</v>
+      </c>
+      <c r="D13" s="3" t="n">
         <v>32.8</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>26.6</v>
+        <v>20.4</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>86.59999999999999</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>12.4</v>
@@ -1515,13 +1517,13 @@
         <v>19.9</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>13.3</v>
+        <v>18.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>22.1</v>
@@ -1541,32 +1543,32 @@
       <c r="Q13" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R13" s="8" t="n">
+      <c r="R13" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="S13" s="3" t="n">
-        <v>25.8</v>
+      <c r="S13" s="8" t="n">
+        <v>21.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>52.7</v>
+        <v>427.4</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="V13" s="8" t="n">
+      <c r="V13" s="3" t="n">
         <v>28</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>29.3</v>
+        <v>29.5</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>77.59999999999999</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1585,7 +1587,7 @@
         <v>190.3</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>30.1</v>
+        <v>30.7</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>21.9</v>
@@ -1596,7 +1598,7 @@
       <c r="G14" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="I14" s="3" t="n">
@@ -1605,9 +1607,7 @@
       <c r="J14" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K14" s="8" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="K14" s="3" t="inlineStr"/>
       <c r="L14" s="3" t="n">
         <v>22.4</v>
       </c>
@@ -1615,25 +1615,25 @@
         <v>22.1</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>264</v>
+        <v>26.4</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>197.3</v>
+        <v>97.3</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>22.4</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="S14" s="8" t="n">
+      <c r="S14" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>189</v>
+        <v>89</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>2.9</v>
@@ -1641,17 +1641,17 @@
       <c r="V14" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W14" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="X14" s="8" t="n">
+      <c r="W14" s="8" t="n">
+        <v>211.6</v>
+      </c>
+      <c r="X14" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>9.1</v>
+        <v>10.9</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1667,15 +1667,15 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>359.6</v>
+        <v>282.8</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>32.5</v>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="E15" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="G15" s="8" t="n">
@@ -1685,30 +1685,30 @@
         <v>19.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>18.4</v>
+        <v>8.4</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K15" s="3" t="n">
-        <v>25.1</v>
+      <c r="K15" s="8" t="n">
+        <v>51.7</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q15" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="3" t="n">
         <v>32</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1718,7 +1718,7 @@
         <v>29.2</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>161.7</v>
+        <v>61.7</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>18.2</v>
@@ -1726,17 +1726,17 @@
       <c r="V15" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W15" s="8" t="n">
+      <c r="W15" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>73.09999999999999</v>
+        <v>738.1</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>10.1</v>
+        <v>100.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1755,13 +1755,13 @@
         <v>1291.2</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>157.9</v>
+        <v>167.9</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1105.5</v>
+        <v>105.5</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>5131.7</v>
+        <v>151.4</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>52.4</v>
@@ -1770,7 +1770,7 @@
         <v>99.2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>111.5</v>
+        <v>11.5</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>19.4</v>
@@ -1785,10 +1785,10 @@
         <v>109.5</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1130.7</v>
+        <v>1230.7</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>27490.1</v>
+        <v>2490.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2.2</v>
@@ -1797,28 +1797,28 @@
         <v>148.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1121.9</v>
+        <v>121.9</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1136.1</v>
+        <v>1136.2</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>331.8</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>176.6</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>133.7</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>1120.7</v>
+        <v>120.7</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>162.5</v>
+        <v>142.5</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1407.4</v>
+        <v>1407.6</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>34.4</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1318.2</v>
+        <v>318.2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>31.6</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>21.1</v>
@@ -1860,48 +1860,50 @@
       <c r="J17" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="L17" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>98</v>
+        <v>398</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>29.7</v>
+        <v>29.1</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="S17" s="8" t="n">
-        <v>28.2</v>
+      <c r="S17" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>166.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v>26.7</v>
+        <v>15.8</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>6.3</v>
       </c>
       <c r="W17" s="8" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X17" s="3" t="n">
-        <v>28.5</v>
+        <v>14.1</v>
+      </c>
+      <c r="X17" s="8" t="n">
+        <v>84.59999999999999</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>181.5</v>
+        <v>81.5</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>16.9</v>
@@ -1920,31 +1922,31 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1368</v>
-      </c>
-      <c r="D18" s="8" t="n">
+        <v>368</v>
+      </c>
+      <c r="D18" s="3" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>24.2</v>
+        <v>21.2</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>286.1</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>20.4</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J18" s="8" t="n">
-        <v>46.3</v>
+      <c r="J18" s="3" t="n">
+        <v>4.3</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>10.4</v>
+        <v>6.4</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>21.4</v>
@@ -1953,10 +1955,10 @@
         <v>21.1</v>
       </c>
       <c r="N18" s="8" t="n">
-        <v>224.8</v>
+        <v>12.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>97.3</v>
+        <v>91.3</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
@@ -1967,26 +1969,26 @@
       <c r="R18" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="S18" s="8" t="n">
+      <c r="S18" s="3" t="n">
         <v>27.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="V18" s="8" t="n">
+      <c r="V18" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>71.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>111</v>
@@ -2005,55 +2007,55 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2260.6</v>
+        <v>265.6</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>308.4</v>
+        <v>30.4</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="3" t="n">
         <v>26.3</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H19" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="L19" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>22</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>86.3</v>
+        <v>26.3</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>197.6</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q19" s="3" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="Q19" s="8" t="n">
         <v>29.9</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>26</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>31.1</v>
+        <v>51.1</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>73.7</v>
@@ -2062,19 +2064,19 @@
         <v>11</v>
       </c>
       <c r="V19" s="8" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="W19" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="X19" s="8" t="n">
-        <v>71.09999999999999</v>
+        <v>16.3</v>
+      </c>
+      <c r="W19" s="8" t="n">
+        <v>289.8</v>
+      </c>
+      <c r="X19" s="3" t="n">
+        <v>24.1</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>89</v>
+        <v>829</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>78.3</v>
+        <v>185.9</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2090,7 +2092,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>365.9</v>
+        <v>3865.9</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>31.4</v>
@@ -2099,7 +2101,7 @@
         <v>21.5</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>26.5</v>
+        <v>8.1</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>19.9</v>
@@ -2107,8 +2109,8 @@
       <c r="H20" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="I20" s="8" t="n">
-        <v>28.1</v>
+      <c r="I20" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>14.5</v>
@@ -2122,26 +2124,26 @@
       <c r="M20" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="N20" s="8" t="n">
-        <v>35.4</v>
+      <c r="N20" s="3" t="n">
+        <v>25.4</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>98</v>
+        <v>928</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="R20" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="R20" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>162.3</v>
+        <v>12.3</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>16.6</v>
@@ -2150,13 +2152,13 @@
         <v>27.3</v>
       </c>
       <c r="W20" s="8" t="n">
-        <v>23.8</v>
+        <v>28.8</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>27.2</v>
+        <v>21.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>715</v>
+        <v>125</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>19.1</v>
@@ -2187,7 +2189,7 @@
         <v>25.9</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>29.5</v>
+        <v>9.5</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>19.6</v>
@@ -2199,22 +2201,22 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>18.6</v>
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>25.6</v>
+        <v>23.6</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>30.6</v>
@@ -2223,7 +2225,7 @@
         <v>26.2</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>31.2</v>
+        <v>91.2</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>71.2</v>
@@ -2231,20 +2233,20 @@
       <c r="U21" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V21" s="8" t="n">
-        <v>78.8</v>
+      <c r="V21" s="3" t="n">
+        <v>27.8</v>
       </c>
       <c r="W21" s="8" t="n">
-        <v>16.6</v>
+        <v>46.6</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>77.3</v>
+        <v>712.3</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>18.4</v>
+        <v>8.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2262,13 +2264,13 @@
       <c r="C22" s="3" t="n">
         <v>399.3</v>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D22" s="3" t="n">
         <v>32.9</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="3" t="n">
         <v>27</v>
       </c>
       <c r="G22" s="3" t="n">
@@ -2278,21 +2280,21 @@
         <v>19.8</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="N22" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="N22" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="O22" s="3" t="n">
@@ -2311,25 +2313,25 @@
         <v>89.3</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>160.5</v>
+        <v>60.5</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>26.8</v>
+        <v>86.5</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>29.1</v>
+        <v>29.4</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>186</v>
+        <v>86</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>14.9</v>
+        <v>1244.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2345,31 +2347,31 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>17439.6</v>
+        <v>8519.6</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>164.5</v>
+        <v>1468.5</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>107.2</v>
+        <v>1074.2</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>132.4</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>250.3</v>
+        <v>50.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1101.8</v>
+        <v>101.8</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>19.3</v>
+        <v>104.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>19.3</v>
+        <v>495.1</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>108.2</v>
@@ -2378,31 +2380,31 @@
         <v>1107</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1126.8</v>
+        <v>126.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1489.4</v>
+        <v>489.4</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>155.7</v>
+        <v>1565.7</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>128.1</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1146.8</v>
+        <v>146.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>325.1</v>
+        <v>3325.1</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>134.4</v>
+        <v>138.4</v>
       </c>
       <c r="W23" s="3" t="n">
         <v>120.3</v>
@@ -2411,10 +2413,10 @@
         <v>140.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>2399</v>
+        <v>399</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>36.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2430,10 +2432,10 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>347.9</v>
+        <v>343.9</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>315.1</v>
+        <v>31.5</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>21.4</v>
@@ -2453,21 +2455,23 @@
       <c r="J24" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="N24" s="8" t="n">
-        <v>22.4</v>
+      <c r="N24" s="3" t="n">
+        <v>25.4</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>97.90000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.4</v>
+        <v>10.4</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>31.1</v>
@@ -2476,10 +2480,10 @@
         <v>25.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>29.4</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>165.1</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>15.9</v>
@@ -2487,17 +2491,17 @@
       <c r="V24" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="W24" s="8" t="n">
+      <c r="W24" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="X24" s="8" t="n">
-        <v>282.2</v>
+        <v>29.2</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>17.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2515,17 +2519,17 @@
       <c r="C25" s="3" t="n">
         <v>106.7</v>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="D25" s="3" t="n">
         <v>26.3</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>23.5</v>
+        <v>23.9</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>20.2</v>
@@ -2537,7 +2541,7 @@
         <v>0.5</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>22.4</v>
@@ -2546,30 +2550,30 @@
         <v>22.1</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>264.4</v>
+        <v>26.4</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>97</v>
+        <v>914</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="R25" s="8" t="n">
-        <v>284.1</v>
-      </c>
-      <c r="S25" s="8" t="n">
+      <c r="R25" s="3" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="S25" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>184.4</v>
-      </c>
-      <c r="U25" s="3" t="inlineStr"/>
-      <c r="V25" s="3" t="n">
-        <v>244.1</v>
-      </c>
+        <v>84.40000000000001</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="V25" s="3" t="inlineStr"/>
       <c r="W25" s="3" t="n">
         <v>22.8</v>
       </c>
@@ -2577,7 +2581,7 @@
         <v>26.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>81.7</v>
+        <v>8417.4</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2600,25 +2604,25 @@
         <v>25.1</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="F26" s="8" t="n">
-        <v>29.1</v>
+        <v>24</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>23.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>14.1</v>
+        <v>12.1</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>10.9</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>16.1</v>
+        <v>6.1</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>21.4</v>
@@ -2627,28 +2631,28 @@
         <v>21.4</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>25.5</v>
+        <v>25.9</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>100</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="R26" s="8" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="S26" s="8" t="n">
-        <v>280.9</v>
+      <c r="R26" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>28</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>192</v>
+        <v>92</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>23.8</v>
@@ -2657,13 +2661,13 @@
         <v>22.8</v>
       </c>
       <c r="X26" s="8" t="n">
-        <v>79.09999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>191.8</v>
+        <v>91.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>2.4</v>
+        <v>124.5</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2679,16 +2683,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2322</v>
+        <v>322</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>20.5</v>
+        <v>3</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="F27" s="8" t="n">
-        <v>25.5</v>
+      <c r="F27" s="3" t="n">
+        <v>85.40000000000001</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>19.9</v>
@@ -2699,12 +2703,14 @@
       <c r="I27" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="n">
+        <v>3.4</v>
+      </c>
       <c r="K27" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>20.7</v>
+        <v>50.3</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>20.5</v>
@@ -2713,7 +2719,7 @@
         <v>24</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0.4</v>
@@ -2722,30 +2728,32 @@
         <v>28.8</v>
       </c>
       <c r="R27" s="8" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S27" s="8" t="n">
-        <v>89</v>
+        <v>16.9</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>73.2</v>
+        <v>23.2</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>26.9</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>24.4</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="X27" s="8" t="n">
-        <v>29</v>
+        <v>289</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>81.8</v>
       </c>
-      <c r="Z27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2760,10 +2768,10 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1290.7</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>51.8</v>
+        <v>290.7</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>91.8</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>20.5</v>
@@ -2774,7 +2782,9 @@
       <c r="G28" s="8" t="n">
         <v>11.3</v>
       </c>
-      <c r="H28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="I28" s="3" t="n">
         <v>2.2</v>
       </c>
@@ -2782,39 +2792,39 @@
         <v>3.8</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="N28" s="8" t="n">
+      <c r="N28" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>297.3</v>
+        <v>97.3</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="R28" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="S28" s="8" t="n">
+      <c r="S28" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>160.2</v>
+        <v>60.2</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="V28" s="8" t="n">
+      <c r="V28" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="W28" s="3" t="n">
@@ -2827,7 +2837,7 @@
         <v>72.59999999999999</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>10.7</v>
+        <v>107.4</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2843,26 +2853,28 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>12146.8</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>31.5</v>
+        <v>246.8</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>16.5</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="G29" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="H29" s="3" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>19.2</v>
+      </c>
       <c r="I29" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.6</v>
+        <v>12.6</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>8.4</v>
@@ -2870,7 +2882,7 @@
       <c r="L29" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="M29" s="8" t="n">
+      <c r="M29" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2883,16 +2895,16 @@
         <v>1.1</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="R29" s="8" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="R29" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="S29" s="8" t="n">
+      <c r="S29" s="3" t="n">
         <v>28</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>87</v>
+        <v>821</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>14.2</v>
@@ -2904,13 +2916,13 @@
         <v>21.3</v>
       </c>
       <c r="X29" s="8" t="n">
-        <v>14.6</v>
+        <v>16.6</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>90.8</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>22.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2932,13 +2944,13 @@
         <v>1145.2</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>1103.2</v>
+        <v>103.2</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>124.2</v>
+        <v>1124.2</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>142</v>
+        <v>42</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>196.6</v>
@@ -2950,52 +2962,52 @@
         <v>111</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>38.8</v>
+        <v>28.8</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>1106.5</v>
+        <v>106.5</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1105.2</v>
+        <v>105.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>123.9</v>
+        <v>125.9</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>487.6</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>11135.8</v>
+        <v>1135.8</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>120.1</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>1140.9</v>
+        <v>140.9</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>396.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>1126.1</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>1115.9</v>
+        <v>115.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>135.9</v>
+        <v>132.9</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>1424.7</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>21.8</v>
+        <v>28.1</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3014,13 +3026,13 @@
         <v>211.2</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>24.8</v>
+        <v>0.9</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>14.8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>8.4</v>
@@ -3034,26 +3046,28 @@
       <c r="J31" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="K31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="L31" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="M31" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="N31" s="8" t="n">
+      <c r="M31" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="N31" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.5</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>10.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="R31" s="8" t="n">
+      <c r="R31" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3062,23 +3076,23 @@
       <c r="T31" s="3" t="n">
         <v>79.40000000000001</v>
       </c>
-      <c r="U31" s="8" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="V31" s="8" t="n">
+      <c r="U31" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="V31" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>27.2</v>
+        <v>97.2</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>145.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3094,7 +3108,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>384.7</v>
+        <v>8816.9</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>31.1</v>
@@ -3112,13 +3126,13 @@
         <v>18</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>12.3</v>
+        <v>2.9</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>20.1</v>
@@ -3126,9 +3140,11 @@
       <c r="M32" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="N32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="n">
+        <v>23.9</v>
+      </c>
       <c r="O32" s="3" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0</v>
@@ -3136,17 +3152,17 @@
       <c r="Q32" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S32" s="3" t="n">
-        <v>27.5</v>
+      <c r="S32" s="8" t="n">
+        <v>72.5</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>161</v>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v>18.5</v>
+        <v>61</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="V32" s="3" t="n">
         <v>27.4</v>
@@ -3154,9 +3170,11 @@
       <c r="W32" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X32" s="3" t="inlineStr"/>
+      <c r="X32" s="3" t="n">
+        <v>97.2</v>
+      </c>
       <c r="Y32" s="3" t="n">
-        <v>174.6</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>19.3</v>
@@ -3183,64 +3201,68 @@
       <c r="E33" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="F33" s="8" t="n">
+      <c r="F33" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="H33" s="8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H33" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L33" s="8" t="n">
-        <v>21.5</v>
+        <v>14.8</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>81.5</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="N33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="n">
+        <v>17.8</v>
+      </c>
       <c r="O33" s="3" t="n">
-        <v>299</v>
+        <v>99</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="R33" s="8" t="n">
-        <v>206.6</v>
-      </c>
-      <c r="S33" s="8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="S33" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>20.9</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="V33" s="8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="V33" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="W33" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="X33" s="3" t="inlineStr"/>
+      <c r="X33" s="3" t="n">
+        <v>28.3</v>
+      </c>
       <c r="Y33" s="3" t="n">
-        <v>861.4</v>
+        <v>86.2</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3258,17 +3280,17 @@
       <c r="C34" s="3" t="n">
         <v>311.6</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="E34" s="8" t="n">
-        <v>11.4</v>
+      <c r="E34" s="3" t="n">
+        <v>21.4</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>26.7</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>20.2</v>
@@ -3277,12 +3299,12 @@
         <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>3.5</v>
+        <v>39.5</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L34" s="8" t="n">
+      <c r="L34" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="M34" s="3" t="n">
@@ -3292,22 +3314,22 @@
         <v>25.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>30.5</v>
+        <v>3</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>25.8</v>
+        <v>23.8</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>30.2</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>169.4</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>13.3</v>
@@ -3322,7 +3344,7 @@
         <v>29.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>82.8</v>
+        <v>182.8</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>16.5</v>
@@ -3346,10 +3368,10 @@
       <c r="D35" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="E35" s="8" t="n">
+      <c r="E35" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="F35" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="G35" s="3" t="n">
@@ -3362,55 +3384,55 @@
         <v>2.4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M35" s="8" t="n">
+      <c r="M35" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>197.2</v>
+        <v>97.2</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>10.7</v>
+        <v>7.1</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="8" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="S35" s="8" t="n">
+      <c r="R35" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="S35" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>1614.3</v>
+        <v>61.3</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="V35" s="8" t="n">
+      <c r="V35" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="W35" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="X35" s="8" t="n">
+      <c r="X35" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>19.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>18.4</v>
+        <v>811.1</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3431,13 +3453,13 @@
       <c r="D36" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="E36" s="8" t="n">
+      <c r="E36" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="G36" s="3" t="n">
+      <c r="G36" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3447,25 +3469,25 @@
         <v>2.4</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K36" s="8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K36" s="3" t="n">
         <v>30.6</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="M36" s="8" t="n">
-        <v>20.1</v>
+      <c r="M36" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>26.2</v>
+        <v>24.2</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>918.5</v>
+        <v>98.5</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>10.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>32.1</v>
@@ -3489,13 +3511,13 @@
         <v>24.6</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>28.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>42.4</v>
+        <v>172</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>211</v>
+        <v>11</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3514,10 +3536,10 @@
         <v>1693.7</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>1155.4</v>
+        <v>155.4</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1102</v>
+        <v>102</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>128.7</v>
@@ -3535,52 +3557,52 @@
         <v>18.1</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>135.6</v>
+        <v>35.6</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>1106</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>1803.2</v>
+        <v>105.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>121.1</v>
+        <v>126.1</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>492.9</v>
+        <v>492.7</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>1.7</v>
+        <v>17.1</v>
       </c>
       <c r="Q37" s="3" t="n">
+        <v>153.1</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>126.2</v>
+      </c>
+      <c r="S37" s="3" t="n">
         <v>143.1</v>
       </c>
-      <c r="R37" s="3" t="n">
-        <v>1126.2</v>
-      </c>
-      <c r="S37" s="3" t="n">
-        <v>1143.1</v>
-      </c>
       <c r="T37" s="3" t="n">
-        <v>13821.8</v>
+        <v>8216.799999999999</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>136.8</v>
+        <v>126.8</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>1142.4</v>
+        <v>102.4</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>398.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>1392.7</v>
+        <v>892.1</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3611,10 +3633,10 @@
         <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>19.3</v>
+        <v>19.8</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.6</v>
@@ -3633,10 +3655,10 @@
         <v>98.5</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>10.3</v>
+        <v>0.3</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>20.7</v>
+        <v>30.7</v>
       </c>
       <c r="R38" s="8" t="n">
         <v>25.2</v>
@@ -3645,25 +3667,25 @@
         <v>28.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>169</v>
+        <v>62</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="V38" s="8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="V38" s="3" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>26.3</v>
+        <v>24.3</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>28.5</v>
+        <v>88.5</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>2.9</v>
+        <v>566.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3679,21 +3701,21 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332.5</v>
+        <v>3232.5</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="E39" s="8" t="n">
+        <v>8218.1</v>
+      </c>
+      <c r="E39" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="F39" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H39" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="H39" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="I39" s="3" t="n">
@@ -3702,11 +3724,13 @@
       <c r="J39" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="8" t="n">
+      <c r="K39" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L39" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="M39" s="8" t="n">
+      <c r="M39" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="N39" s="3" t="n">
@@ -3716,37 +3740,37 @@
         <v>99</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>31.9</v>
+        <v>11.9</v>
       </c>
       <c r="R39" s="8" t="n">
-        <v>126</v>
-      </c>
-      <c r="S39" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="S39" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>163.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>17.3</v>
+        <v>11.9</v>
       </c>
       <c r="V39" s="8" t="n">
-        <v>24.9</v>
+        <v>49.1</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>23.2</v>
+        <v>22.2</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>27.6</v>
+        <v>2.7</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>288.2</v>
+        <v>88.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>13.6</v>
+        <v>8.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3762,10 +3786,10 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1453.1</v>
+        <v>1534.1</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>32.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>18.8</v>
@@ -3780,33 +3804,33 @@
         <v>18.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>12.7</v>
+        <v>2.1</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M40" s="8" t="n">
+      <c r="M40" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>28.6</v>
+        <v>22.6</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>1797.8</v>
+        <v>97.8</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>32.8</v>
       </c>
-      <c r="R40" s="8" t="n">
+      <c r="R40" s="3" t="n">
         <v>26</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3819,7 +3843,7 @@
         <v>20.2</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>24.8</v>
+        <v>27.8</v>
       </c>
       <c r="W40" s="8" t="n">
         <v>23.8</v>
@@ -3828,10 +3852,10 @@
         <v>26.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>72</v>
+        <v>22.8</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>10.4</v>
+        <v>101.6</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3847,7 +3871,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>269.6</v>
+        <v>965.6</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>31.6</v>
@@ -3856,7 +3880,7 @@
         <v>19.6</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>85.59999999999999</v>
+        <v>25.6</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>12</v>
@@ -3870,8 +3894,8 @@
       <c r="J41" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="K41" s="8" t="n">
-        <v>43.6</v>
+      <c r="K41" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>19.9</v>
@@ -3883,10 +3907,10 @@
         <v>23</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>199</v>
+        <v>98</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>22.3</v>
@@ -3898,25 +3922,25 @@
         <v>24.9</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>192.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>12</v>
+        <v>2.8</v>
       </c>
       <c r="V41" s="8" t="n">
-        <v>816.6</v>
-      </c>
-      <c r="W41" s="8" t="n">
-        <v>83.40000000000001</v>
+        <v>46.6</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>23.4</v>
       </c>
       <c r="X41" s="8" t="n">
-        <v>28</v>
+        <v>9218</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>190.5</v>
+        <v>90.5</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>2.9</v>
+        <v>18.9</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3932,15 +3956,15 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1236.3</v>
+        <v>836.3</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>31.6</v>
       </c>
-      <c r="E42" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F42" s="8" t="n">
+      <c r="E42" s="8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F42" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="G42" s="8" t="n">
@@ -3950,12 +3974,12 @@
         <v>20</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K42" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K42" s="8" t="n">
         <v>28.1</v>
       </c>
       <c r="L42" s="3" t="n">
@@ -3964,43 +3988,45 @@
       <c r="M42" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="N42" s="8" t="n">
-        <v>26</v>
+      <c r="N42" s="3" t="n">
+        <v>26.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>199</v>
+        <v>1899</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="8" t="n">
+      <c r="Q42" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="R42" s="8" t="n">
+      <c r="R42" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="S42" s="8" t="n">
+      <c r="S42" s="3" t="n">
         <v>29.3</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>197.7</v>
+        <v>97.7</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v>21.7</v>
+        <v>0.8</v>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v>822.9</v>
       </c>
       <c r="W42" s="8" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>28.2</v>
+        <v>82.5</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>88.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>190.6</v>
-      </c>
-      <c r="Z42" s="3" t="inlineStr"/>
+        <v>90.59999999999999</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>2.9</v>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -4024,7 +4050,7 @@
         <v>21.3</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>25.7</v>
+        <v>29.1</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>8.699999999999999</v>
@@ -4033,13 +4059,13 @@
         <v>19.8</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>3.7</v>
+        <v>13.7</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>21.6</v>
@@ -4051,7 +4077,7 @@
         <v>25.6</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>0.2</v>
@@ -4060,22 +4086,22 @@
         <v>29.1</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="S43" s="3" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v>79.8</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>24.7</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="W43" s="8" t="n">
+        <v>41.4</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>29.1</v>
@@ -4084,7 +4110,7 @@
         <v>18</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>18.2</v>
+        <v>198.2</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4100,7 +4126,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>365.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>22.6</v>
@@ -4108,53 +4134,53 @@
       <c r="E44" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="F44" s="8" t="n">
+      <c r="F44" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="H44" s="8" t="n">
-        <v>19.4</v>
+      <c r="H44" s="3" t="n">
+        <v>89.40000000000001</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>19.6</v>
+        <v>9.6</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>28.3</v>
+        <v>22.3</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="N44" s="8" t="n">
+      <c r="N44" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R44" s="3" t="n">
+      <c r="R44" s="8" t="n">
         <v>26.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>30.1</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="U44" s="8" t="n">
-        <v>18.6</v>
+      <c r="U44" s="3" t="n">
+        <v>8.6</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>28.5</v>
@@ -4162,14 +4188,14 @@
       <c r="W44" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="X44" s="8" t="n">
-        <v>32.2</v>
+      <c r="X44" s="3" t="n">
+        <v>82.8</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>84.40000000000001</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>166</v>
+        <v>16</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4184,65 +4210,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="3" t="inlineStr"/>
+      <c r="C45" s="3" t="n">
+        <v>2026.2</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>19165.6</v>
+      </c>
       <c r="E45" s="3" t="n">
-        <v>1121</v>
+        <v>1128</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>1796.1</v>
+        <v>2026.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>109.1</v>
+        <v>9.1</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>114.7</v>
+        <v>1114.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>10.7</v>
+        <v>1101</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>18.4</v>
+        <v>118.4</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>172.3</v>
+        <v>743.1</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>1166.9</v>
+        <v>11665.9</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>122.9</v>
+        <v>128.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>148.7</v>
+        <v>1148.8</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>293.8</v>
+        <v>292.8</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1752.8</v>
+        <v>172.8</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>149.1</v>
-      </c>
-      <c r="S45" s="3" t="inlineStr"/>
-      <c r="T45" s="3" t="inlineStr"/>
+        <v>1469.1</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>174.1</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>1450.8</v>
+      </c>
       <c r="U45" s="3" t="n">
-        <v>168.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>138.1</v>
-      </c>
-      <c r="W45" s="3" t="inlineStr"/>
-      <c r="X45" s="3" t="inlineStr"/>
+        <v>158.1</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>172.2</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>84.5</v>
+      </c>
       <c r="Y45" s="3" t="n">
-        <v>3503.7</v>
+        <v>900.1</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>9316</v>
+        <v>56</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4258,19 +4296,19 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>2337.6</v>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E46" s="8" t="n">
+        <v>237.6</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E46" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="F46" s="8" t="n">
+      <c r="F46" s="3" t="n">
         <v>26</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>11.5</v>
+        <v>21.5</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>19.1</v>
@@ -4279,13 +4317,15 @@
         <v>1.7</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
+        <v>3.1</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="L46" s="8" t="n">
         <v>11.1</v>
       </c>
-      <c r="M46" s="8" t="n">
+      <c r="M46" s="3" t="n">
         <v>20</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4295,37 +4335,37 @@
         <v>99</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R46" s="8" t="n">
-        <v>216.8</v>
-      </c>
-      <c r="S46" s="8" t="n">
+      <c r="R46" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="S46" s="3" t="n">
         <v>29</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>729</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V46" s="8" t="n">
-        <v>643.4</v>
-      </c>
-      <c r="W46" s="8" t="n">
+      <c r="V46" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="W46" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>28.1</v>
+        <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>283.9</v>
+        <v>83.8</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>15.7</v>
+        <v>62.5</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>136.2</v>
+        <v>186.2</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>28.1</v>
@@ -745,16 +745,16 @@
         <v>20</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>81.7</v>
+        <v>87.2</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1.7</v>
+        <v>11.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>2.9</v>
@@ -778,13 +778,13 @@
         <v>0.2</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>22.1</v>
+        <v>27.1</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>68.90000000000001</v>
@@ -796,13 +796,13 @@
         <v>25.2</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>82.8</v>
+        <v>22.8</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>181.8</v>
+        <v>81.8</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>5.8</v>
@@ -821,9 +821,9 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>203.8</v>
-      </c>
-      <c r="D5" s="8" t="n">
+        <v>403.8</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>32.6</v>
       </c>
       <c r="E5" s="3" t="n">
@@ -845,7 +845,7 @@
         <v>5.5</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>18.9</v>
@@ -857,7 +857,7 @@
         <v>21.6</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>909</v>
+        <v>99</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0.2</v>
@@ -883,11 +883,11 @@
       <c r="W5" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X5" s="8" t="n">
-        <v>72.8</v>
+      <c r="X5" s="3" t="n">
+        <v>27.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>141.1</v>
+        <v>7174</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>8.199999999999999</v>
@@ -906,13 +906,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>122.3</v>
+        <v>422.3</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>34.2</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>12.2</v>
+        <v>28.8</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>26.5</v>
@@ -921,7 +921,7 @@
         <v>15.4</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>184.6</v>
+        <v>15.2</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>14.6</v>
@@ -944,8 +944,8 @@
       <c r="O6" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="P6" s="8" t="n">
-        <v>80</v>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>32.7</v>
@@ -957,22 +957,22 @@
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>22.8</v>
+        <v>92.8</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>20.4</v>
+        <v>20.7</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="W6" s="8" t="n">
-        <v>31.7</v>
+        <v>28.1</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>23.7</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>16614.1</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>13.2</v>
@@ -991,16 +991,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6472.5</v>
+        <v>472.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>21</v>
+        <v>34.8</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>72</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>15.4</v>
@@ -1009,10 +1009,10 @@
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>47.9</v>
+        <v>84.7</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.9</v>
+        <v>7.9</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>34.2</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>27.1</v>
@@ -1047,7 +1047,7 @@
       <c r="U7" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="V7" s="8" t="n">
+      <c r="V7" s="3" t="n">
         <v>29.5</v>
       </c>
       <c r="W7" s="3" t="n">
@@ -1060,7 +1060,7 @@
         <v>66.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>15.8</v>
+        <v>13.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>30.9</v>
@@ -1112,7 +1112,7 @@
         <v>24</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>96.5</v>
+        <v>296.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.8</v>
@@ -1142,7 +1142,7 @@
         <v>26.1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>20.6</v>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1781.2</v>
+        <v>1783.2</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>164.8</v>
@@ -1170,19 +1170,19 @@
         <v>96.90000000000001</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1301.7</v>
+        <v>230.8</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>12.8</v>
+        <v>27.5</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>30.9</v>
@@ -1197,40 +1197,40 @@
         <v>112.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>894.2</v>
+        <v>494.2</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1179.6</v>
+        <v>149.6</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>122.9</v>
+        <v>121.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>155.1</v>
+        <v>135.7</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>329.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>132.8</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1116.8</v>
+        <v>116.8</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>133.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>388.8</v>
+        <v>3788.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>141.6</v>
+        <v>41.6</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1246,13 +1246,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8188.5</v>
+        <v>35.4</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>33</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>19.4</v>
+        <v>19.8</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>26.2</v>
@@ -1261,15 +1261,17 @@
         <v>13.6</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>11.9</v>
+        <v>17.9</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
+        <v>5.5</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>20</v>
       </c>
@@ -1285,14 +1287,14 @@
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="8" t="n">
         <v>29.9</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>94.40000000000001</v>
+        <v>24.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>27.8</v>
+        <v>27.1</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>66</v>
@@ -1306,14 +1308,14 @@
       <c r="W10" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="X10" s="8" t="n">
-        <v>16.2</v>
+      <c r="X10" s="3" t="n">
+        <v>26.7</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>72.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>18.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1329,7 +1331,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1265.6</v>
+        <v>265.6</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>30.1</v>
@@ -1347,7 +1349,7 @@
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.8</v>
@@ -1362,10 +1364,10 @@
         <v>20.9</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>927.3</v>
+        <v>21.3</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>0.6</v>
@@ -1374,31 +1376,31 @@
         <v>29.9</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="S11" s="8" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="S11" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>720.6</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="V11" s="8" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="W11" s="8" t="n">
-        <v>16.9</v>
+      <c r="V11" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>94.90000000000001</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>2894</v>
+        <v>894</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>11.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1414,10 +1416,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>347.1</v>
+        <v>242.1</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>91.8</v>
+        <v>81.8</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>82.59999999999999</v>
@@ -1431,8 +1433,8 @@
       <c r="H12" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="I12" s="8" t="n">
-        <v>227.1</v>
+      <c r="I12" s="3" t="n">
+        <v>2.7</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>14.6</v>
@@ -1443,14 +1445,14 @@
       <c r="L12" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="M12" s="8" t="n">
-        <v>350.5</v>
-      </c>
-      <c r="N12" s="8" t="n">
-        <v>17.9</v>
+      <c r="M12" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>27.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>927.5</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.5</v>
@@ -1462,10 +1464,10 @@
         <v>24.9</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>21.1</v>
+        <v>27.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>51.8</v>
+        <v>59.8</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>19.8</v>
@@ -1483,7 +1485,7 @@
         <v>76.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>21.6</v>
+        <v>81.7</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1510,7 @@
         <v>20.4</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>26.6</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>12.4</v>
@@ -1517,10 +1519,10 @@
         <v>19.9</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>18.3</v>
+        <v>3.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
@@ -1546,11 +1548,11 @@
       <c r="R13" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="S13" s="8" t="n">
-        <v>21.8</v>
+      <c r="S13" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>427.4</v>
+        <v>52.7</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>23.3</v>
@@ -1562,7 +1564,7 @@
         <v>24.8</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>77.59999999999999</v>
@@ -1586,8 +1588,8 @@
       <c r="C14" s="3" t="n">
         <v>190.3</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>30.7</v>
+      <c r="D14" s="8" t="n">
+        <v>7.1</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>21.9</v>
@@ -1602,12 +1604,14 @@
         <v>20.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
+        <v>82.09999999999999</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="L14" s="3" t="n">
         <v>22.4</v>
       </c>
@@ -1641,8 +1645,8 @@
       <c r="V14" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W14" s="8" t="n">
-        <v>211.6</v>
+      <c r="W14" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>25.5</v>
@@ -1650,9 +1654,7 @@
       <c r="Y14" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="Z14" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="Z14" s="3" t="inlineStr"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1667,7 +1669,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>282.8</v>
+        <v>359.6</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>32.5</v>
@@ -1685,28 +1687,28 @@
         <v>19.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K15" s="8" t="n">
-        <v>51.7</v>
+      <c r="K15" s="3" t="n">
+        <v>23.7</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="M15" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>32</v>
@@ -1733,10 +1735,10 @@
         <v>28.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>738.1</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>100.6</v>
+        <v>10.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1752,16 +1754,16 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1291.2</v>
+        <v>1221.2</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>167.9</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>105.5</v>
+        <v>1255.1</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>151.4</v>
+        <v>131.9</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>52.4</v>
@@ -1779,16 +1781,16 @@
         <v>36.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1110.6</v>
+        <v>110.6</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>109.5</v>
+        <v>109.8</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>1230.7</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>2490.1</v>
+        <v>1490.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2.2</v>
@@ -1797,10 +1799,10 @@
         <v>148.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>121.9</v>
+        <v>1221.9</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1136.2</v>
+        <v>1136.1</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>331.8</v>
@@ -1840,7 +1842,7 @@
         <v>318.2</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>31.6</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>21.1</v>
@@ -1855,13 +1857,13 @@
         <v>19.8</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>12.3</v>
+        <v>2.3</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K17" s="3" t="n">
-        <v>1.1</v>
+      <c r="K17" s="8" t="n">
+        <v>6</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>22.1</v>
@@ -1873,13 +1875,13 @@
         <v>26.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>398</v>
+        <v>928</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>29.1</v>
+        <v>29.7</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>24.4</v>
@@ -1891,16 +1893,16 @@
         <v>66.40000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>15.8</v>
+        <v>15.3</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W17" s="8" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="X17" s="8" t="n">
-        <v>84.59999999999999</v>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>28.5</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>81.5</v>
@@ -1925,17 +1927,15 @@
         <v>368</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>32.1</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="F18" s="8" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="F18" s="3" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="n">
         <v>80.40000000000001</v>
       </c>
@@ -1943,10 +1943,10 @@
         <v>2.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K18" s="8" t="n">
-        <v>6.4</v>
+        <v>14.3</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>10.4</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>21.4</v>
@@ -1954,11 +1954,11 @@
       <c r="M18" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="N18" s="8" t="n">
-        <v>12.8</v>
+      <c r="N18" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>91.3</v>
+        <v>97.3</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
@@ -1966,14 +1966,14 @@
       <c r="Q18" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="R18" s="8" t="n">
+      <c r="R18" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>27.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>20</v>
@@ -1988,10 +1988,10 @@
         <v>21.9</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2021,8 +2021,8 @@
       <c r="G19" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H19" s="3" t="n">
-        <v>21.4</v>
+      <c r="H19" s="8" t="n">
+        <v>91.40000000000001</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.6</v>
@@ -2046,7 +2046,7 @@
         <v>97.59999999999999</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="Q19" s="8" t="n">
         <v>29.9</v>
@@ -2055,7 +2055,7 @@
         <v>26</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>51.1</v>
+        <v>31.1</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>73.7</v>
@@ -2063,20 +2063,20 @@
       <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="8" t="n">
-        <v>16.3</v>
+      <c r="V19" s="3" t="n">
+        <v>24.3</v>
       </c>
       <c r="W19" s="8" t="n">
-        <v>289.8</v>
+        <v>28.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>24.1</v>
+        <v>27.1</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>829</v>
+        <v>89</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>185.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2092,16 +2092,16 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3865.9</v>
+        <v>365.9</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>8.1</v>
+      <c r="E20" s="8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>28.5</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>19.9</v>
@@ -2110,13 +2110,13 @@
         <v>20.6</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>21.6</v>
@@ -2128,19 +2128,19 @@
         <v>25.4</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>928</v>
+        <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>20.9</v>
+        <v>30.7</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="S20" s="3" t="n">
-        <v>27.5</v>
+      <c r="S20" s="8" t="n">
+        <v>17.5</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>12.3</v>
@@ -2151,17 +2151,17 @@
       <c r="V20" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="W20" s="8" t="n">
-        <v>28.8</v>
+      <c r="W20" s="3" t="n">
+        <v>22.8</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>21.2</v>
+        <v>27.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>125</v>
+        <v>725</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2179,8 +2179,8 @@
       <c r="C21" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D21" s="3" t="n">
-        <v>30.7</v>
+      <c r="D21" s="8" t="n">
+        <v>7.2</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>21.2</v>
@@ -2207,10 +2207,10 @@
         <v>21.6</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>21.9</v>
+        <v>21.5</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>23.6</v>
+        <v>25.6</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>99</v>
@@ -2225,7 +2225,7 @@
         <v>26.2</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>91.2</v>
+        <v>31.2</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>71.2</v>
@@ -2237,13 +2237,13 @@
         <v>27.8</v>
       </c>
       <c r="W21" s="8" t="n">
-        <v>46.6</v>
+        <v>26.6</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>712.3</v>
+        <v>72.3</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>8.4</v>
@@ -2274,7 +2274,7 @@
         <v>27</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>19.8</v>
@@ -2286,13 +2286,13 @@
         <v>4.3</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>24.7</v>
@@ -2307,7 +2307,7 @@
         <v>32.4</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>25.9</v>
+        <v>29.9</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>89.3</v>
@@ -2316,22 +2316,22 @@
         <v>60.5</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="V22" s="3" t="n">
-        <v>86.5</v>
+        <v>19.2</v>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v>26.5</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X22" s="8" t="n">
-        <v>29.4</v>
+      <c r="X22" s="3" t="n">
+        <v>29.7</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>86</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>1244.9</v>
+        <v>144.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2347,19 +2347,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>8519.6</v>
+        <v>1739.6</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1468.5</v>
+        <v>167.5</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1074.2</v>
+        <v>107.2</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>132.4</v>
+        <v>138.8</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>50.3</v>
+        <v>20.3</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>101.8</v>
@@ -2368,10 +2368,10 @@
         <v>10.9</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>104.5</v>
+        <v>10.4</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>495.1</v>
+        <v>49.1</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>108.2</v>
@@ -2389,7 +2389,7 @@
         <v>2.2</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1565.7</v>
+        <v>155.7</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>128.1</v>
@@ -2398,16 +2398,16 @@
         <v>146.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>3325.1</v>
+        <v>325.1</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>138.4</v>
+        <v>134.4</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>120.3</v>
+        <v>20.3</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>140.8</v>
@@ -2416,7 +2416,7 @@
         <v>399</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>362.5</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>343.9</v>
+        <v>343.2</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>31.5</v>
@@ -2441,7 +2441,7 @@
         <v>21.4</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>10.1</v>
@@ -2450,13 +2450,13 @@
         <v>20.4</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>3.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>21.6</v>
@@ -2477,10 +2477,10 @@
         <v>31.1</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>25.6</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>29.4</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>65.09999999999999</v>
@@ -2494,14 +2494,14 @@
       <c r="W24" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="X24" s="8" t="n">
-        <v>29.2</v>
+      <c r="X24" s="3" t="n">
+        <v>23.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>79.8</v>
+        <v>2981.3</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2526,10 +2526,10 @@
         <v>20.6</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>20.2</v>
@@ -2541,7 +2541,7 @@
         <v>0.5</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>23.4</v>
+        <v>23.7</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>22.4</v>
@@ -2553,7 +2553,7 @@
         <v>26.4</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>914</v>
+        <v>97</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0.7</v>
@@ -2562,7 +2562,7 @@
         <v>26.2</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>24.1</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>28.7</v>
@@ -2571,17 +2571,19 @@
         <v>84.40000000000001</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="V25" s="3" t="inlineStr"/>
+        <v>5.3</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>14.4</v>
+      </c>
       <c r="W25" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>8417.4</v>
+        <v>8781.700000000001</v>
       </c>
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2604,22 +2606,22 @@
         <v>25.1</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>12.1</v>
+        <v>14.1</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>6.1</v>
@@ -2631,7 +2633,7 @@
         <v>21.4</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>100</v>
@@ -2643,13 +2645,13 @@
         <v>24.3</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>28</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>92</v>
+        <v>192</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>2.4</v>
@@ -2660,14 +2662,14 @@
       <c r="W26" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X26" s="8" t="n">
-        <v>71.09999999999999</v>
+      <c r="X26" s="3" t="n">
+        <v>27.1</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>91.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>124.5</v>
+        <v>2.4</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2686,13 +2688,13 @@
         <v>322</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3</v>
+        <v>30.5</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>25.5</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>19.9</v>
@@ -2710,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>20.5</v>
@@ -2727,8 +2729,8 @@
       <c r="Q27" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="R27" s="8" t="n">
-        <v>16.9</v>
+      <c r="R27" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>29</v>
@@ -2739,20 +2741,20 @@
       <c r="U27" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="V27" s="3" t="n">
-        <v>86.90000000000001</v>
+      <c r="V27" s="8" t="n">
+        <v>826.9</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>94.40000000000001</v>
+        <v>24.4</v>
       </c>
       <c r="X27" s="8" t="n">
-        <v>289</v>
+        <v>89</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>81.8</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>12.4</v>
+        <v>6.4</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2770,8 +2772,8 @@
       <c r="C28" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D28" s="8" t="n">
-        <v>91.8</v>
+      <c r="D28" s="3" t="n">
+        <v>31.8</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>20.5</v>
@@ -2804,10 +2806,10 @@
         <v>24.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>97.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>31.2</v>
@@ -2837,7 +2839,7 @@
         <v>72.59999999999999</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>107.4</v>
+        <v>10.7</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2855,14 +2857,14 @@
       <c r="C29" s="3" t="n">
         <v>246.8</v>
       </c>
-      <c r="D29" s="8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>20.5</v>
+      <c r="D29" s="3" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>80.5</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="G29" s="8" t="n">
         <v>11</v>
@@ -2874,7 +2876,7 @@
         <v>1.6</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>8.4</v>
@@ -2895,7 +2897,7 @@
         <v>1.1</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>25.3</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>23.6</v>
@@ -2904,10 +2906,10 @@
         <v>28</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>14.2</v>
+        <v>94.2</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>22.4</v>
@@ -2916,7 +2918,7 @@
         <v>21.3</v>
       </c>
       <c r="X29" s="8" t="n">
-        <v>16.6</v>
+        <v>14.6</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>90.8</v>
@@ -2941,19 +2943,19 @@
         <v>11056.2</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1145.2</v>
+        <v>145.2</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>103.2</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1124.2</v>
+        <v>124.2</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>42</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>196.6</v>
+        <v>296.6</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>7.1</v>
@@ -2962,7 +2964,7 @@
         <v>111</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>28.8</v>
+        <v>328.8</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>106.5</v>
@@ -2971,7 +2973,7 @@
         <v>105.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>125.9</v>
+        <v>123.9</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>487.6</v>
@@ -2983,31 +2985,29 @@
         <v>1135.8</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>120.1</v>
+        <v>120.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>140.9</v>
+        <v>1240.9</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>396.8</v>
       </c>
-      <c r="U30" s="3" t="n">
-        <v>18</v>
-      </c>
+      <c r="U30" s="3" t="inlineStr"/>
       <c r="V30" s="3" t="n">
-        <v>1126.1</v>
+        <v>126.1</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>115.8</v>
+        <v>115.9</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>132.9</v>
+        <v>135.9</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>1424.7</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>28.1</v>
+        <v>85.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3026,13 +3026,13 @@
         <v>211.2</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>14.8</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>8.4</v>
@@ -3047,7 +3047,7 @@
         <v>2.2</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>21.3</v>
@@ -3059,7 +3059,7 @@
         <v>24.8</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>97.5</v>
+        <v>927.5</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>0.6</v>
@@ -3077,7 +3077,7 @@
         <v>79.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>18.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>25.2</v>
@@ -3086,13 +3086,13 @@
         <v>23.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>97.2</v>
+        <v>27.2</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>24.9</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3108,16 +3108,16 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>8816.9</v>
+        <v>384.7</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>31.1</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>19.3</v>
+        <v>29.3</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>25.2</v>
+        <v>23.2</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>11.8</v>
@@ -3126,7 +3126,7 @@
         <v>18</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>4.6</v>
@@ -3141,7 +3141,7 @@
         <v>20.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>100</v>
@@ -3155,26 +3155,26 @@
       <c r="R32" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S32" s="8" t="n">
-        <v>72.5</v>
+      <c r="S32" s="3" t="n">
+        <v>27.5</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>61</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>27.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>23.8</v>
+        <v>83.8</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>97.2</v>
+        <v>27.2</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>7641.6</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>19.3</v>
@@ -3220,13 +3220,13 @@
         <v>14.8</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>81.5</v>
+        <v>21.5</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>17.8</v>
+        <v>23.9</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>99</v>
@@ -3235,16 +3235,16 @@
         <v>0.2</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>22.9</v>
+        <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>20.6</v>
+        <v>28.6</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>20.9</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>11.5</v>
@@ -3252,17 +3252,17 @@
       <c r="V33" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>28.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>86.2</v>
+        <v>26.1</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>12.5</v>
+        <v>144.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3286,11 +3286,11 @@
       <c r="E34" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="F34" s="8" t="n">
+      <c r="F34" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>20.2</v>
@@ -3299,7 +3299,7 @@
         <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>39.5</v>
+        <v>9.5</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.2</v>
@@ -3320,10 +3320,10 @@
         <v>0.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>3</v>
+        <v>30.5</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>23.8</v>
+        <v>25.8</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>30.2</v>
@@ -3344,7 +3344,7 @@
         <v>29.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>182.8</v>
+        <v>82.8</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>16.5</v>
@@ -3365,13 +3365,13 @@
       <c r="C35" s="3" t="n">
         <v>353.4</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="8" t="n">
         <v>31.1</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F35" s="8" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="F35" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="G35" s="3" t="n">
@@ -3402,16 +3402,16 @@
         <v>97.2</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="3" t="n">
-        <v>24.9</v>
+      <c r="R35" s="8" t="n">
+        <v>46.9</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>27.8</v>
+        <v>21.8</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>61.3</v>
@@ -3420,7 +3420,7 @@
         <v>17.4</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>21.8</v>
+        <v>27.8</v>
       </c>
       <c r="W35" s="8" t="n">
         <v>16.6</v>
@@ -3429,10 +3429,10 @@
         <v>28.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>811.1</v>
+        <v>8.4</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>24.2</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>98.5</v>
+        <v>97.5</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.6</v>
@@ -3507,17 +3507,17 @@
       <c r="V36" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W36" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X36" s="8" t="n">
-        <v>83.90000000000001</v>
+      <c r="W36" s="8" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>28.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>172</v>
+        <v>72</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>11</v>
+        <v>1411</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3563,10 +3563,10 @@
         <v>1106</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>105.2</v>
+        <v>103.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>126.1</v>
+        <v>124.1</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>492.7</v>
@@ -3575,7 +3575,7 @@
         <v>17.1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>153.1</v>
+        <v>153.7</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>126.2</v>
@@ -3584,25 +3584,25 @@
         <v>143.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>8216.799999999999</v>
+        <v>324.8</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>11.7</v>
+        <v>19.7</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>126.8</v>
+        <v>136.8</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>102.4</v>
+        <v>122.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>398.2</v>
+        <v>3928.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>892.1</v>
+        <v>39.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>10.6</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>2</v>
@@ -3660,20 +3660,20 @@
       <c r="Q38" s="3" t="n">
         <v>30.7</v>
       </c>
-      <c r="R38" s="8" t="n">
+      <c r="R38" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>27.4</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>24.3</v>
@@ -3685,7 +3685,7 @@
         <v>78</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>566.1</v>
+        <v>7.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>3232.5</v>
-      </c>
-      <c r="D39" s="8" t="n">
-        <v>8218.1</v>
+        <v>332.5</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>31.9</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>20.2</v>
@@ -3715,7 +3715,7 @@
       <c r="G39" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="H39" s="3" t="n">
+      <c r="H39" s="8" t="n">
         <v>19.3</v>
       </c>
       <c r="I39" s="3" t="n">
@@ -3725,7 +3725,7 @@
         <v>3</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>21</v>
@@ -3743,9 +3743,9 @@
         <v>0.2</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="R39" s="8" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="R39" s="3" t="n">
         <v>26</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3755,13 +3755,13 @@
         <v>163.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v>49.1</v>
+        <v>11.3</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>22.2</v>
+        <v>23.2</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>2.7</v>
@@ -3770,7 +3770,7 @@
         <v>88.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>8.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1534.1</v>
+        <v>153.7</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>22.9</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>18.8</v>
@@ -3804,10 +3804,10 @@
         <v>18.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
@@ -3837,7 +3837,7 @@
         <v>29.3</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>39.2</v>
+        <v>59.2</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>20.2</v>
@@ -3845,14 +3845,14 @@
       <c r="V40" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W40" s="8" t="n">
+      <c r="W40" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X40" s="3" t="n">
-        <v>26.9</v>
+      <c r="X40" s="8" t="n">
+        <v>86.90000000000001</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>22.8</v>
+        <v>72</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>101.6</v>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>965.6</v>
+        <v>8985.6</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>31.6</v>
@@ -3907,7 +3907,7 @@
         <v>23</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.2</v>
@@ -3918,29 +3918,29 @@
       <c r="R41" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="S41" s="3" t="n">
-        <v>24.9</v>
+      <c r="S41" s="8" t="n">
+        <v>16.9</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v>46.6</v>
+        <v>2</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>22.6</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="X41" s="8" t="n">
-        <v>9218</v>
+      <c r="X41" s="3" t="n">
+        <v>98</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>90.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>18.9</v>
+        <v>8.9</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3961,13 +3961,13 @@
       <c r="D42" s="3" t="n">
         <v>31.6</v>
       </c>
-      <c r="E42" s="8" t="n">
-        <v>3.9</v>
+      <c r="E42" s="3" t="n">
+        <v>20.3</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="G42" s="8" t="n">
+      <c r="G42" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -3976,11 +3976,11 @@
       <c r="I42" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="J42" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K42" s="8" t="n">
-        <v>28.1</v>
+      <c r="J42" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>28.4</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>21.9</v>
@@ -3989,10 +3989,10 @@
         <v>21.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>1899</v>
+        <v>89</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.2</v>
@@ -4012,14 +4012,14 @@
       <c r="U42" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="V42" s="8" t="n">
-        <v>822.9</v>
-      </c>
-      <c r="W42" s="8" t="n">
-        <v>82.5</v>
+      <c r="V42" s="3" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="X42" s="8" t="n">
-        <v>88.2</v>
+        <v>828.2</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>90.59999999999999</v>
@@ -4050,7 +4050,7 @@
         <v>21.3</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>29.1</v>
+        <v>24.7</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>8.699999999999999</v>
@@ -4062,7 +4062,7 @@
         <v>2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>13.7</v>
+        <v>3.7</v>
       </c>
       <c r="K43" s="3" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>29.1</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="S43" s="3" t="n">
         <v>80.40000000000001</v>
@@ -4100,17 +4100,17 @@
       <c r="V43" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="W43" s="8" t="n">
-        <v>41.4</v>
+      <c r="W43" s="3" t="n">
+        <v>24.7</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>198.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>365.9</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>22.6</v>
+        <v>226.1</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>21.3</v>
@@ -4140,8 +4140,8 @@
       <c r="G44" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="H44" s="3" t="n">
-        <v>89.40000000000001</v>
+      <c r="H44" s="8" t="n">
+        <v>19.4</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>1.9</v>
@@ -4152,11 +4152,11 @@
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="3" t="n">
-        <v>22.3</v>
+      <c r="L44" s="8" t="n">
+        <v>82.3</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>22.3</v>
+        <v>82.3</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>26.9</v>
@@ -4165,31 +4165,31 @@
         <v>100</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R44" s="8" t="n">
+      <c r="R44" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>30.4</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>162</v>
+        <v>62</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>8.6</v>
+        <v>18.6</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="X44" s="3" t="n">
-        <v>82.8</v>
+      <c r="X44" s="8" t="n">
+        <v>28.2</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>84.40000000000001</v>
@@ -4214,73 +4214,73 @@
         <v>2026.2</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>19165.6</v>
+        <v>1901.6</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>1128</v>
+        <v>11298.6</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>2026.1</v>
+        <v>226.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>9.1</v>
+        <v>2.1</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>1114.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>1101</v>
+        <v>11</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>118.4</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>743.1</v>
+        <v>783.6</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>11665.9</v>
+        <v>1166.5</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>128.9</v>
+        <v>123.9</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>1148.8</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>292.8</v>
+        <v>293.8</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>172.8</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>1469.1</v>
+        <v>149.1</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>174.1</v>
+        <v>121.1</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>1450.8</v>
+        <v>1230</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="V45" s="3" t="n">
         <v>158.1</v>
       </c>
       <c r="W45" s="3" t="n">
+        <v>128.2</v>
+      </c>
+      <c r="X45" s="3" t="n">
         <v>172.2</v>
       </c>
-      <c r="X45" s="3" t="n">
-        <v>84.5</v>
-      </c>
       <c r="Y45" s="3" t="n">
-        <v>900.1</v>
+        <v>503.4</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
       <c r="F46" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="G46" s="8" t="n">
+      <c r="G46" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="H46" s="3" t="n">
@@ -4319,11 +4319,9 @@
       <c r="J46" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" s="8" t="n">
-        <v>11.1</v>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>20</v>
@@ -4332,7 +4330,7 @@
         <v>24.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>0.2</v>
@@ -4347,7 +4345,7 @@
         <v>29</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>22.9</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.4</v>
@@ -4362,10 +4360,10 @@
         <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>83.8</v>
+        <v>88.8</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>62.5</v>
+        <v>6.2</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_decimal_place_correction.xlsx
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>186.2</v>
+        <v>13.6</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>28.1</v>
+        <v>28.8</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>20</v>
@@ -748,19 +748,19 @@
         <v>24.3</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>18.2</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>88.2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>11.8</v>
+        <v>1.7</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>20.2</v>
@@ -798,7 +798,7 @@
       <c r="W4" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X4" s="3" t="n">
+      <c r="X4" s="8" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>403.8</v>
+        <v>240.3</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>32.6</v>
@@ -835,8 +835,8 @@
       <c r="G5" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>16.8</v>
+      <c r="H5" s="8" t="n">
+        <v>416.8</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>3.5</v>
@@ -887,7 +887,7 @@
         <v>27.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>7174</v>
+        <v>77</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>8.199999999999999</v>
@@ -912,7 +912,7 @@
         <v>34.2</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>28.8</v>
+        <v>18.8</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>26.5</v>
@@ -920,11 +920,11 @@
       <c r="G6" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="H6" s="8" t="n">
-        <v>15.2</v>
+      <c r="H6" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>7.2</v>
@@ -957,13 +957,13 @@
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>92.8</v>
+        <v>155.8</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>28.1</v>
+        <v>28.7</v>
       </c>
       <c r="W6" s="3" t="n">
         <v>23.7</v>
@@ -994,13 +994,13 @@
         <v>472.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>34.8</v>
+        <v>3.4</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="F7" s="8" t="n">
-        <v>72</v>
+      <c r="F7" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>15.4</v>
@@ -1009,7 +1009,7 @@
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>84.7</v>
+        <v>64.7</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>7.9</v>
@@ -1024,37 +1024,37 @@
         <v>20.1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>23.5</v>
+        <v>2.3</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>100</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>34.2</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>20.6</v>
+        <v>50.6</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>26.5</v>
+        <v>2.6</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>29.5</v>
+        <v>2.9</v>
       </c>
       <c r="W7" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>27.3</v>
+        <v>2.7</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>66.2</v>
@@ -1091,15 +1091,15 @@
         <v>14</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" s="8" t="n">
         <v>30.9</v>
       </c>
       <c r="L8" s="3" t="n">
@@ -1112,7 +1112,7 @@
         <v>24</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>296.5</v>
+        <v>96.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.8</v>
@@ -1145,7 +1145,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>20.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1783.2</v>
+        <v>178.3</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>164.8</v>
@@ -1170,7 +1170,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>230.8</v>
+        <v>130.8</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>67.90000000000001</v>
@@ -1179,13 +1179,13 @@
         <v>89.40000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>100.2</v>
@@ -1194,13 +1194,13 @@
         <v>99.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>112.8</v>
+        <v>118.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>494.2</v>
+        <v>494.5</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>149.6</v>
@@ -1212,10 +1212,10 @@
         <v>135.7</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>329.9</v>
+        <v>2329.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>132.8</v>
@@ -1227,7 +1227,7 @@
         <v>133.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>3788.8</v>
+        <v>388.8</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>41.6</v>
@@ -1246,13 +1246,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>35.4</v>
+        <v>356.7</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>33</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>26.2</v>
@@ -1269,9 +1269,7 @@
       <c r="J10" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K10" s="3" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
         <v>20</v>
       </c>
@@ -1287,7 +1285,7 @@
       <c r="P10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q10" s="8" t="n">
+      <c r="Q10" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="R10" s="3" t="n">
@@ -1312,7 +1310,7 @@
         <v>26.7</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>72.8</v>
+        <v>77.8</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>8.300000000000001</v>
@@ -1349,7 +1347,7 @@
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.6</v>
+        <v>11.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.8</v>
@@ -1367,7 +1365,7 @@
         <v>24.5</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>21.3</v>
+        <v>97.3</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>0.6</v>
@@ -1376,7 +1374,7 @@
         <v>29.9</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>23.5</v>
+        <v>25.5</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>29.8</v>
@@ -1391,16 +1389,16 @@
         <v>27.1</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>24.9</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>30.1</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>894</v>
+        <v>84</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>5.8</v>
+        <v>159.8</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1416,13 +1414,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>242.1</v>
+        <v>347.1</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>81.8</v>
+        <v>31.8</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>22.6</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>27.2</v>
@@ -1437,7 +1435,7 @@
         <v>2.7</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1452,7 +1450,7 @@
         <v>27.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>927.5</v>
+        <v>27.5</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.5</v>
@@ -1467,13 +1465,13 @@
         <v>27.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>59.8</v>
+        <v>58.8</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>21.9</v>
+        <v>27.9</v>
       </c>
       <c r="W12" s="3" t="n">
         <v>24.6</v>
@@ -1485,7 +1483,7 @@
         <v>76.7</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>81.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1507,7 +1505,7 @@
         <v>32.8</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>26.6</v>
@@ -1522,7 +1520,7 @@
         <v>3.3</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
@@ -1561,7 +1559,7 @@
         <v>28</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>24.8</v>
+        <v>2.4</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>29.3</v>
@@ -1570,7 +1568,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>18.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1588,8 +1586,8 @@
       <c r="C14" s="3" t="n">
         <v>190.3</v>
       </c>
-      <c r="D14" s="8" t="n">
-        <v>7.1</v>
+      <c r="D14" s="3" t="n">
+        <v>30.7</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>21.9</v>
@@ -1604,10 +1602,10 @@
         <v>20.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>11.1</v>
@@ -1628,13 +1626,13 @@
         <v>0.7</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>22.4</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>24.2</v>
+        <v>202.1</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>89</v>
@@ -1654,7 +1652,9 @@
       <c r="Y14" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="Z14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1693,19 +1693,19 @@
         <v>3.9</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>23.7</v>
+        <v>25.7</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>21.6</v>
+        <v>28.6</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>25.8</v>
+        <v>29.8</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>100.2</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0</v>
@@ -1754,19 +1754,19 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1221.2</v>
+        <v>1591.2</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>167.9</v>
+        <v>157.9</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1255.1</v>
+        <v>105.5</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>131.9</v>
+        <v>131.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>52.4</v>
+        <v>352.4</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>99.2</v>
@@ -1781,16 +1781,16 @@
         <v>36.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>110.6</v>
+        <v>1110.6</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>109.8</v>
+        <v>109.5</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1230.7</v>
+        <v>130.7</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1490.1</v>
+        <v>2490.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2.2</v>
@@ -1799,7 +1799,7 @@
         <v>148.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1221.9</v>
+        <v>121.9</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>1136.1</v>
@@ -1814,13 +1814,13 @@
         <v>133.7</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>120.7</v>
+        <v>2120.7</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>142.5</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1407.6</v>
+        <v>407.4</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>34.4</v>
@@ -1841,7 +1841,7 @@
       <c r="C17" s="3" t="n">
         <v>318.2</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="8" t="n">
         <v>31.6</v>
       </c>
       <c r="E17" s="3" t="n">
@@ -1862,8 +1862,8 @@
       <c r="J17" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K17" s="8" t="n">
-        <v>6</v>
+      <c r="K17" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>22.1</v>
@@ -1875,10 +1875,10 @@
         <v>26.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>928</v>
+        <v>298</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>29.7</v>
@@ -1890,15 +1890,15 @@
         <v>22.2</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>66.40000000000001</v>
+        <v>166.4</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>15.3</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W17" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="W17" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1908,7 +1908,7 @@
         <v>81.5</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1933,23 +1933,25 @@
         <v>21.2</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
+        <v>26.7</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>10.9</v>
+      </c>
       <c r="H18" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>20.4</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>10.4</v>
+        <v>4</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>21.4</v>
+        <v>24.4</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>21.1</v>
@@ -1958,12 +1960,12 @@
         <v>24.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>97.3</v>
+        <v>197.3</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q18" s="3" t="n">
+      <c r="Q18" s="8" t="n">
         <v>32.1</v>
       </c>
       <c r="R18" s="3" t="n">
@@ -1973,7 +1975,7 @@
         <v>27.7</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>20</v>
@@ -1985,10 +1987,10 @@
         <v>24.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>21.9</v>
+        <v>27.9</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>171.7</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>11</v>
@@ -2021,8 +2023,8 @@
       <c r="G19" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H19" s="8" t="n">
-        <v>91.40000000000001</v>
+      <c r="H19" s="3" t="n">
+        <v>21.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>1.6</v>
@@ -2046,7 +2048,7 @@
         <v>97.59999999999999</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>10.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q19" s="8" t="n">
         <v>29.9</v>
@@ -2066,8 +2068,8 @@
       <c r="V19" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="W19" s="8" t="n">
-        <v>28.9</v>
+      <c r="W19" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>27.1</v>
@@ -2076,7 +2078,7 @@
         <v>89</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2094,17 +2096,17 @@
       <c r="C20" s="3" t="n">
         <v>365.9</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="E20" s="8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>28.5</v>
+      <c r="E20" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>26.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>19.9</v>
+        <v>29.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>20.6</v>
@@ -2113,7 +2115,7 @@
         <v>2.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0</v>
@@ -2125,13 +2127,13 @@
         <v>21.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>25.4</v>
+        <v>25.1</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.4</v>
+        <v>10.4</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>30.7</v>
@@ -2139,29 +2141,29 @@
       <c r="R20" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="S20" s="8" t="n">
-        <v>17.5</v>
+      <c r="S20" s="3" t="n">
+        <v>27.5</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>12.3</v>
+        <v>62.3</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>27.3</v>
+        <v>2.7</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>22.8</v>
+        <v>23.8</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>725</v>
+        <v>85</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>9.1</v>
+        <v>19.1</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2179,8 +2181,8 @@
       <c r="C21" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D21" s="8" t="n">
-        <v>7.2</v>
+      <c r="D21" s="3" t="n">
+        <v>30.7</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>21.2</v>
@@ -2236,8 +2238,8 @@
       <c r="V21" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W21" s="8" t="n">
-        <v>26.6</v>
+      <c r="W21" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>28.9</v>
@@ -2262,7 +2264,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>399.3</v>
+        <v>2399.3</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>32.9</v>
@@ -2274,7 +2276,7 @@
         <v>27</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>11.8</v>
+        <v>1.1</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>19.8</v>
@@ -2286,7 +2288,7 @@
         <v>4.3</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2.7</v>
+        <v>7.7</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>21.3</v>
@@ -2298,16 +2300,16 @@
         <v>24.7</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>97.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>32.4</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>29.9</v>
+        <v>25.9</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>89.3</v>
@@ -2318,7 +2320,7 @@
       <c r="U22" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="V22" s="8" t="n">
+      <c r="V22" s="3" t="n">
         <v>26.5</v>
       </c>
       <c r="W22" s="3" t="n">
@@ -2331,7 +2333,7 @@
         <v>86</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>144.9</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2350,16 +2352,16 @@
         <v>1739.6</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>167.5</v>
+        <v>157.5</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>107.2</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>138.8</v>
+        <v>132.4</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>20.3</v>
+        <v>50.3</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>101.8</v>
@@ -2368,16 +2370,16 @@
         <v>10.9</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>10.4</v>
+        <v>19.3</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>49.1</v>
+        <v>19.3</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>108.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1107</v>
+        <v>10.7</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>126.8</v>
@@ -2398,16 +2400,16 @@
         <v>146.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>325.1</v>
+        <v>325.7</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>79.40000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>134.4</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>20.3</v>
+        <v>1120.3</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>140.8</v>
@@ -2416,7 +2418,7 @@
         <v>399</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>362.5</v>
+        <v>36.7</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2432,7 +2434,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>343.2</v>
+        <v>347.9</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>31.5</v>
@@ -2441,7 +2443,7 @@
         <v>21.4</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>26.3</v>
+        <v>26.5</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>10.1</v>
@@ -2455,9 +2457,7 @@
       <c r="J24" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>21.6</v>
       </c>
@@ -2477,10 +2477,10 @@
         <v>31.1</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>25.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>29.4</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>65.09999999999999</v>
@@ -2495,13 +2495,13 @@
         <v>24.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>23.2</v>
+        <v>22.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>2981.3</v>
+        <v>79.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>7.3</v>
+        <v>17.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
       <c r="E25" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="F25" s="8" t="n">
         <v>23.5</v>
       </c>
       <c r="G25" s="3" t="n">
@@ -2547,7 +2547,7 @@
         <v>22.4</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>22.1</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>26.4</v>
@@ -2571,10 +2571,10 @@
         <v>84.40000000000001</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v>14.4</v>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>24.4</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>22.8</v>
@@ -2583,9 +2583,11 @@
         <v>26.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>8781.700000000001</v>
-      </c>
-      <c r="Z25" s="3" t="inlineStr"/>
+        <v>87.7</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>3.8</v>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2606,7 +2608,7 @@
         <v>25.1</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>23.1</v>
@@ -2624,7 +2626,7 @@
         <v>0.7</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>21.4</v>
@@ -2651,10 +2653,10 @@
         <v>28</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>192</v>
+        <v>92</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>23.8</v>
@@ -2669,7 +2671,7 @@
         <v>91.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>2.4</v>
+        <v>12.4</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2688,7 +2690,7 @@
         <v>322</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>30.5</v>
+        <v>20.5</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>20.6</v>
@@ -2697,7 +2699,7 @@
         <v>25.5</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>19.9</v>
+        <v>9.9</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>19.1</v>
@@ -2712,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>50.4</v>
+        <v>20.7</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>20.5</v>
@@ -2721,7 +2723,7 @@
         <v>24</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>98</v>
+        <v>298</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0.4</v>
@@ -2736,25 +2738,25 @@
         <v>29</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>23.2</v>
+        <v>73.2</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="V27" s="8" t="n">
-        <v>826.9</v>
+      <c r="V27" s="3" t="n">
+        <v>26.9</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="X27" s="8" t="n">
-        <v>89</v>
+      <c r="X27" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>81.8</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>6.4</v>
+        <v>16.4</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2773,7 +2775,7 @@
         <v>290.7</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>31.8</v>
+        <v>23.8</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>20.5</v>
@@ -2806,10 +2808,10 @@
         <v>24.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>31.2</v>
@@ -2818,7 +2820,7 @@
         <v>24.8</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>27.2</v>
+        <v>2.7</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>60.2</v>
@@ -2860,17 +2862,17 @@
       <c r="D29" s="3" t="n">
         <v>31.5</v>
       </c>
-      <c r="E29" s="8" t="n">
-        <v>80.5</v>
+      <c r="E29" s="3" t="n">
+        <v>20.5</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="G29" s="8" t="n">
+      <c r="G29" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="H29" s="3" t="n">
-        <v>19.2</v>
+      <c r="H29" s="8" t="n">
+        <v>69.2</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1.6</v>
@@ -2882,7 +2884,7 @@
         <v>8.4</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>21.1</v>
+        <v>20.1</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>20.6</v>
@@ -2891,13 +2893,13 @@
         <v>23.9</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>95.3</v>
+        <v>2.5</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>1.1</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>25.3</v>
+        <v>82.5</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>23.6</v>
@@ -2906,10 +2908,10 @@
         <v>28</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>827</v>
+        <v>27</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>94.2</v>
+        <v>4.2</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>22.4</v>
@@ -2917,11 +2919,11 @@
       <c r="W29" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="X29" s="8" t="n">
-        <v>14.6</v>
+      <c r="X29" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>90.8</v>
+        <v>912.1</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>2.5</v>
@@ -2940,7 +2942,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>11056.2</v>
+        <v>1056.2</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>145.2</v>
@@ -2961,10 +2963,10 @@
         <v>7.1</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>328.8</v>
+        <v>38.8</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>106.5</v>
@@ -2976,7 +2978,7 @@
         <v>123.9</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>487.6</v>
+        <v>2487.6</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>2.8</v>
@@ -2988,14 +2990,16 @@
         <v>120.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>1240.9</v>
+        <v>140.9</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>396.8</v>
       </c>
-      <c r="U30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V30" s="3" t="n">
-        <v>126.1</v>
+        <v>1126.1</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>115.9</v>
@@ -3004,10 +3008,10 @@
         <v>135.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>1424.7</v>
+        <v>1428.7</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>85.8</v>
+        <v>25.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3026,12 +3030,12 @@
         <v>211.2</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="F31" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F31" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
@@ -3046,9 +3050,7 @@
       <c r="J31" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
         <v>21.3</v>
       </c>
@@ -3059,7 +3061,7 @@
         <v>24.8</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>927.5</v>
+        <v>97.5</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>0.6</v>
@@ -3077,19 +3079,19 @@
         <v>79.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="V31" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="V31" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="8" t="n">
         <v>23.2</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>84.90000000000001</v>
+        <v>24.9</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>5.2</v>
@@ -3114,10 +3116,10 @@
         <v>31.1</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>29.3</v>
+        <v>19.3</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>23.2</v>
+        <v>25.2</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>11.8</v>
@@ -3141,7 +3143,7 @@
         <v>20.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>23.5</v>
+        <v>23.9</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>100</v>
@@ -3165,19 +3167,19 @@
         <v>17.5</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>27.4</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>83.8</v>
+        <v>23.8</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>7641.6</v>
+        <v>746.6</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>19.3</v>
+        <v>195.3</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3195,8 +3197,8 @@
       <c r="C33" s="3" t="n">
         <v>213.3</v>
       </c>
-      <c r="D33" s="3" t="n">
-        <v>29.2</v>
+      <c r="D33" s="8" t="n">
+        <v>229.2</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>19.6</v>
@@ -3211,13 +3213,13 @@
         <v>18.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>14.8</v>
+        <v>4.8</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>21.5</v>
@@ -3226,7 +3228,7 @@
         <v>21.4</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>23.9</v>
+        <v>25.4</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>99</v>
@@ -3238,7 +3240,7 @@
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>28.6</v>
+        <v>21.6</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.2</v>
@@ -3259,10 +3261,10 @@
         <v>28.3</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>26.1</v>
+        <v>0.1</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>144.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3280,7 +3282,7 @@
       <c r="C34" s="3" t="n">
         <v>311.6</v>
       </c>
-      <c r="D34" s="8" t="n">
+      <c r="D34" s="3" t="n">
         <v>31.9</v>
       </c>
       <c r="E34" s="3" t="n">
@@ -3299,7 +3301,7 @@
         <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>9.5</v>
+        <v>3.5</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.2</v>
@@ -3314,7 +3316,7 @@
         <v>25.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
@@ -3322,8 +3324,8 @@
       <c r="Q34" s="3" t="n">
         <v>30.5</v>
       </c>
-      <c r="R34" s="3" t="n">
-        <v>25.8</v>
+      <c r="R34" s="8" t="n">
+        <v>35.8</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>30.2</v>
@@ -3344,7 +3346,7 @@
         <v>29.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>82.8</v>
+        <v>82</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>16.5</v>
@@ -3363,13 +3365,13 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>353.4</v>
+        <v>353.1</v>
       </c>
       <c r="D35" s="8" t="n">
         <v>31.1</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>30.8</v>
+        <v>20.8</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>25.9</v>
@@ -3399,7 +3401,7 @@
         <v>25.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>97.2</v>
+        <v>297.2</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0.7</v>
@@ -3411,7 +3413,7 @@
         <v>46.9</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>21.8</v>
+        <v>27.8</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>61.3</v>
@@ -3429,7 +3431,7 @@
         <v>28.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>3.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8.4</v>
@@ -3459,7 +3461,7 @@
       <c r="F36" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="G36" s="8" t="n">
+      <c r="G36" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3484,7 +3486,7 @@
         <v>24.2</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>97.5</v>
+        <v>925.1</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.6</v>
@@ -3507,17 +3509,17 @@
       <c r="V36" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W36" s="8" t="n">
-        <v>46.6</v>
+      <c r="W36" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>28.8</v>
+        <v>28.3</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>72</v>
+        <v>172</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1411</v>
+        <v>111</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3536,7 +3538,7 @@
         <v>1693.7</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>155.4</v>
+        <v>14155.4</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>102</v>
@@ -3563,7 +3565,7 @@
         <v>1106</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>103.2</v>
+        <v>105.2</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>124.1</v>
@@ -3572,7 +3574,7 @@
         <v>492.7</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>17.1</v>
+        <v>1.7</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>153.7</v>
@@ -3581,13 +3583,13 @@
         <v>126.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>143.1</v>
+        <v>1143.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>324.8</v>
+        <v>2324.8</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>19.7</v>
+        <v>79.7</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>136.8</v>
@@ -3599,10 +3601,10 @@
         <v>122.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>3928.2</v>
+        <v>392.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>39.7</v>
+        <v>139.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3621,7 +3623,7 @@
         <v>338.7</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>31</v>
+        <v>31.9</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>20.4</v>
@@ -3652,7 +3654,7 @@
         <v>24.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>98.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>0.3</v>
@@ -3667,22 +3669,22 @@
         <v>28.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>27.4</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>88.5</v>
+        <v>28.5</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>78</v>
+        <v>29.1</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>7.9</v>
@@ -3712,10 +3714,10 @@
       <c r="F39" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="G39" s="8" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="H39" s="8" t="n">
+      <c r="G39" s="3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H39" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="I39" s="3" t="n">
@@ -3725,7 +3727,7 @@
         <v>3</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>21</v>
@@ -3743,7 +3745,7 @@
         <v>0.2</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>31.9</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>26</v>
@@ -3755,22 +3757,22 @@
         <v>163.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>11.3</v>
+        <v>18.3</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>2.7</v>
+        <v>27.5</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>88.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>23.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3786,10 +3788,10 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>153.7</v>
+        <v>1453.7</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>22.9</v>
+        <v>32.9</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>18.8</v>
@@ -3848,14 +3850,14 @@
       <c r="W40" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X40" s="8" t="n">
-        <v>86.90000000000001</v>
+      <c r="X40" s="3" t="n">
+        <v>26.9</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>72</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>101.6</v>
+        <v>10.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3871,15 +3873,15 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>8985.6</v>
-      </c>
-      <c r="D41" s="3" t="n">
+        <v>265.6</v>
+      </c>
+      <c r="D41" s="8" t="n">
         <v>31.6</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="F41" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="G41" s="3" t="n">
@@ -3895,7 +3897,7 @@
         <v>1.6</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>19.9</v>
@@ -3918,8 +3920,8 @@
       <c r="R41" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="S41" s="8" t="n">
-        <v>16.9</v>
+      <c r="S41" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>92.3</v>
@@ -3927,20 +3929,20 @@
       <c r="U41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="V41" s="3" t="n">
-        <v>22.6</v>
+      <c r="V41" s="8" t="n">
+        <v>11.6</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>23.4</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>190.5</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3956,7 +3958,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>836.3</v>
+        <v>236.3</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>31.6</v>
@@ -3976,11 +3978,11 @@
       <c r="I42" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="J42" s="8" t="n">
-        <v>8</v>
+      <c r="J42" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>28.4</v>
+        <v>28.7</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>21.9</v>
@@ -4007,26 +4009,24 @@
         <v>29.3</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>97.7</v>
+        <v>97.2</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>22.7</v>
+        <v>24.7</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="X42" s="8" t="n">
-        <v>828.2</v>
+        <v>23.5</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>28.2</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="Z42" s="3" t="n">
-        <v>2.9</v>
-      </c>
+      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -4050,7 +4050,7 @@
         <v>21.3</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>24.7</v>
+        <v>25.7</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>8.699999999999999</v>
@@ -4098,13 +4098,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>21.8</v>
+        <v>27.8</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>29.1</v>
+        <v>34.1</v>
       </c>
       <c r="Y43" s="3" t="n">
         <v>78</v>
@@ -4129,7 +4129,7 @@
         <v>365.9</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>226.1</v>
+        <v>22.6</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>21.3</v>
@@ -4141,22 +4141,22 @@
         <v>11.3</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>19.4</v>
+        <v>49.4</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="8" t="n">
-        <v>82.3</v>
+      <c r="L44" s="3" t="n">
+        <v>22.3</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>82.3</v>
+        <v>22.3</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>26.9</v>
@@ -4183,16 +4183,16 @@
         <v>18.6</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="X44" s="8" t="n">
-        <v>28.2</v>
+      <c r="X44" s="3" t="n">
+        <v>32.2</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>184.4</v>
       </c>
       <c r="Z44" s="3" t="n">
         <v>16</v>
@@ -4211,40 +4211,40 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2026.2</v>
+        <v>202.6</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>1901.6</v>
+        <v>190.6</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>11298.6</v>
+        <v>1121.5</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>226.1</v>
+        <v>156.3</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>2.1</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>1114.2</v>
+        <v>1114.7</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>11</v>
+        <v>101.2</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>118.4</v>
+        <v>18.4</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>783.6</v>
+        <v>18.3</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>1166.5</v>
+        <v>126.3</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>123.9</v>
+        <v>10122.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1148.8</v>
+        <v>1148.7</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>293.8</v>
@@ -4259,10 +4259,10 @@
         <v>149.1</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>121.1</v>
+        <v>174.1</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>1230</v>
+        <v>2430</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>68.59999999999999</v>
@@ -4271,16 +4271,16 @@
         <v>158.1</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>128.2</v>
+        <v>144.9</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>172.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>503.4</v>
+        <v>583.7</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
       <c r="C46" s="3" t="n">
         <v>237.6</v>
       </c>
-      <c r="D46" s="8" t="n">
+      <c r="D46" s="3" t="n">
         <v>31.7</v>
       </c>
       <c r="E46" s="3" t="n">
@@ -4308,7 +4308,7 @@
         <v>26</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>21.5</v>
+        <v>11.5</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>19.1</v>
@@ -4319,23 +4319,25 @@
       <c r="J46" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="L46" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="Q46" s="8" t="n">
         <v>28.8</v>
       </c>
       <c r="R46" s="3" t="n">
@@ -4345,7 +4347,7 @@
         <v>29</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>22.9</v>
+        <v>75</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>11.4</v>
@@ -4360,10 +4362,10 @@
         <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>88.8</v>
+        <v>823.9</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_decimal_place_correction.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -736,10 +727,10 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>13.6</v>
+        <v>186.2</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>20</v>
@@ -750,8 +741,8 @@
       <c r="G4" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="H4" s="8" t="n">
-        <v>88.2</v>
+      <c r="H4" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>1.7</v>
@@ -760,7 +751,7 @@
         <v>2.9</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>20.2</v>
@@ -798,7 +789,7 @@
       <c r="W4" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X4" s="8" t="n">
+      <c r="X4" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="Y4" s="3" t="n">
@@ -821,7 +812,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>240.3</v>
+        <v>403.5</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>32.6</v>
@@ -835,8 +826,8 @@
       <c r="G5" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="H5" s="8" t="n">
-        <v>416.8</v>
+      <c r="H5" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>3.5</v>
@@ -906,7 +897,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>422.3</v>
+        <v>22.3</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>34.2</v>
@@ -957,7 +948,7 @@
         <v>28.6</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>155.8</v>
+        <v>55.8</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>20.7</v>
@@ -994,13 +985,13 @@
         <v>472.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.4</v>
+        <v>34.7</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>15.4</v>
@@ -1009,10 +1000,10 @@
         <v>18.2</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>64.7</v>
+        <v>4.7</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
@@ -1024,7 +1015,7 @@
         <v>20.1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>2.3</v>
+        <v>23.5</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>100</v>
@@ -1036,7 +1027,7 @@
         <v>34.2</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>2.5</v>
+        <v>25.5</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>27.1</v>
@@ -1045,16 +1036,16 @@
         <v>50.6</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>2.6</v>
+        <v>26.5</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>2.9</v>
+        <v>29.5</v>
       </c>
       <c r="W7" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>2.7</v>
+        <v>27.3</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>66.2</v>
@@ -1090,7 +1081,7 @@
       <c r="G8" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H8" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I8" s="3" t="n">
@@ -1099,7 +1090,7 @@
       <c r="J8" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K8" s="8" t="n">
+      <c r="K8" s="3" t="n">
         <v>30.9</v>
       </c>
       <c r="L8" s="3" t="n">
@@ -1145,7 +1136,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0.6</v>
+        <v>20.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1194,7 +1185,7 @@
         <v>99.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>118.8</v>
+        <v>15.8</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>494.5</v>
@@ -1212,7 +1203,7 @@
         <v>135.7</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>2329.9</v>
+        <v>329.9</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>81</v>
@@ -1347,7 +1338,7 @@
         <v>18.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>2.8</v>
@@ -1398,7 +1389,7 @@
         <v>84</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>159.8</v>
+        <v>5.7</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1417,7 +1408,7 @@
         <v>347.1</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>31.8</v>
+        <v>31.2</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>22.6</v>
@@ -1450,7 +1441,7 @@
         <v>27.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>27.5</v>
+        <v>97.5</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.5</v>
@@ -1465,7 +1456,7 @@
         <v>27.1</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>58.8</v>
+        <v>57.8</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>19.8</v>
@@ -1505,7 +1496,7 @@
         <v>32.8</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>26.6</v>
@@ -1559,7 +1550,7 @@
         <v>28</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>2.4</v>
+        <v>24.8</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>29.3</v>
@@ -1568,7 +1559,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1680,7 +1671,7 @@
       <c r="F15" s="3" t="n">
         <v>26.7</v>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="G15" s="3" t="n">
         <v>11.7</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1696,13 +1687,13 @@
         <v>25.7</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>28.6</v>
+        <v>21.6</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>29.8</v>
+        <v>25.8</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>100</v>
@@ -1766,7 +1757,7 @@
         <v>131.7</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>352.4</v>
+        <v>52.4</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>99.2</v>
@@ -1781,7 +1772,7 @@
         <v>36.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1110.6</v>
+        <v>110.6</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>109.5</v>
@@ -1790,7 +1781,7 @@
         <v>130.7</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>2490.1</v>
+        <v>490.1</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2.2</v>
@@ -1802,7 +1793,7 @@
         <v>121.9</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1136.1</v>
+        <v>136.1</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>331.8</v>
@@ -1814,7 +1805,7 @@
         <v>133.7</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>2120.7</v>
+        <v>120.7</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>142.5</v>
@@ -1841,7 +1832,7 @@
       <c r="C17" s="3" t="n">
         <v>318.2</v>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D17" s="3" t="n">
         <v>31.6</v>
       </c>
       <c r="E17" s="3" t="n">
@@ -1875,10 +1866,10 @@
         <v>26.1</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>298</v>
+        <v>98</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>29.7</v>
@@ -1887,10 +1878,10 @@
         <v>24.4</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>22.2</v>
+        <v>27.2</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>166.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>15.3</v>
@@ -1898,7 +1889,7 @@
       <c r="V17" s="3" t="n">
         <v>26.7</v>
       </c>
-      <c r="W17" s="8" t="n">
+      <c r="W17" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1960,12 +1951,12 @@
         <v>24.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>197.3</v>
+        <v>97.3</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q18" s="8" t="n">
+      <c r="Q18" s="3" t="n">
         <v>32.1</v>
       </c>
       <c r="R18" s="3" t="n">
@@ -1990,7 +1981,7 @@
         <v>27.9</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>171.7</v>
+        <v>71.7</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>11</v>
@@ -2050,7 +2041,7 @@
       <c r="P19" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q19" s="8" t="n">
+      <c r="Q19" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="R19" s="3" t="n">
@@ -2078,7 +2069,7 @@
         <v>89</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>12.3</v>
+        <v>3.3</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2096,17 +2087,17 @@
       <c r="C20" s="3" t="n">
         <v>365.9</v>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="3" t="n">
         <v>31.4</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="3" t="n">
         <v>26.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>29.9</v>
+        <v>9.9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>20.6</v>
@@ -2127,13 +2118,13 @@
         <v>21.4</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>25.1</v>
+        <v>25.4</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>30.7</v>
@@ -2151,7 +2142,7 @@
         <v>16.6</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>2.7</v>
+        <v>27.3</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>23.8</v>
@@ -2160,10 +2151,10 @@
         <v>27.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2245,7 +2236,7 @@
         <v>28.9</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>72.3</v>
+        <v>77.3</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>8.4</v>
@@ -2264,7 +2255,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2399.3</v>
+        <v>399.3</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>32.9</v>
@@ -2276,7 +2267,7 @@
         <v>27</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1.1</v>
+        <v>11.8</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>19.8</v>
@@ -2300,10 +2291,10 @@
         <v>24.7</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>32.4</v>
@@ -2312,7 +2303,7 @@
         <v>25.9</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>89.3</v>
+        <v>29.3</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>60.5</v>
@@ -2333,7 +2324,7 @@
         <v>86</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2379,13 +2370,13 @@
         <v>108.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>10.7</v>
+        <v>107</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>126.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>489.4</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>2.2</v>
@@ -2409,7 +2400,7 @@
         <v>134.4</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>1120.3</v>
+        <v>120.3</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>140.8</v>
@@ -2471,7 +2462,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>31.1</v>
@@ -2480,7 +2471,7 @@
         <v>25.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>29.4</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>65.09999999999999</v>
@@ -2495,13 +2486,13 @@
         <v>24.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>22.2</v>
+        <v>28.2</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>17.3</v>
+        <v>7.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2525,7 +2516,7 @@
       <c r="E25" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="F25" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="G25" s="3" t="n">
@@ -2571,7 +2562,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>24.4</v>
@@ -2602,19 +2593,19 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>290</v>
+        <v>90</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>14.1</v>
+        <v>4.1</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>19.2</v>
@@ -2656,7 +2647,7 @@
         <v>92</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>2.8</v>
+        <v>22.9</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>23.8</v>
@@ -2671,7 +2662,7 @@
         <v>91.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2690,7 +2681,7 @@
         <v>322</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>20.5</v>
+        <v>30.5</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>20.6</v>
@@ -2723,7 +2714,7 @@
         <v>24</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>298</v>
+        <v>98</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0.4</v>
@@ -2756,7 +2747,7 @@
         <v>81.8</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>16.4</v>
+        <v>6.4</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2775,7 +2766,7 @@
         <v>290.7</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>23.8</v>
+        <v>31.8</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>20.5</v>
@@ -2783,7 +2774,7 @@
       <c r="F28" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="G28" s="8" t="n">
+      <c r="G28" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="H28" s="3" t="n">
@@ -2820,7 +2811,7 @@
         <v>24.8</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>2.7</v>
+        <v>27.2</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>60.2</v>
@@ -2871,8 +2862,8 @@
       <c r="G29" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="H29" s="8" t="n">
-        <v>69.2</v>
+      <c r="H29" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1.6</v>
@@ -2884,7 +2875,7 @@
         <v>8.4</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>20.1</v>
+        <v>21.1</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>20.6</v>
@@ -2893,13 +2884,13 @@
         <v>23.9</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>2.5</v>
+        <v>95.3</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>1.1</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>82.5</v>
+        <v>25.3</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>23.6</v>
@@ -2908,7 +2899,7 @@
         <v>28</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>4.2</v>
@@ -2957,7 +2948,7 @@
         <v>42</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>296.6</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>7.1</v>
@@ -2978,13 +2969,13 @@
         <v>123.9</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>2487.6</v>
+        <v>487.6</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>1135.8</v>
+        <v>135.8</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>120.7</v>
@@ -2999,7 +2990,7 @@
         <v>19.5</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>1126.1</v>
+        <v>126.1</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>115.9</v>
@@ -3008,7 +2999,7 @@
         <v>135.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>1428.7</v>
+        <v>24.7</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>25.8</v>
@@ -3035,7 +3026,7 @@
       <c r="E31" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="F31" s="8" t="n">
+      <c r="F31" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="G31" s="3" t="n">
@@ -3079,19 +3070,19 @@
         <v>79.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="V31" s="8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="V31" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="W31" s="8" t="n">
+      <c r="W31" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>24.9</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>5.2</v>
@@ -3124,7 +3115,7 @@
       <c r="G32" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="H32" s="8" t="n">
+      <c r="H32" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I32" s="3" t="n">
@@ -3143,7 +3134,7 @@
         <v>20.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>100</v>
@@ -3176,10 +3167,10 @@
         <v>27.2</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>746.6</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>195.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3197,8 +3188,8 @@
       <c r="C33" s="3" t="n">
         <v>213.3</v>
       </c>
-      <c r="D33" s="8" t="n">
-        <v>229.2</v>
+      <c r="D33" s="3" t="n">
+        <v>29.2</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>19.6</v>
@@ -3213,7 +3204,7 @@
         <v>18.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>1.6</v>
@@ -3231,7 +3222,7 @@
         <v>25.4</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>99</v>
+        <v>99.7</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0.2</v>
@@ -3240,7 +3231,7 @@
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>21.6</v>
+        <v>22.6</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.2</v>
@@ -3264,7 +3255,7 @@
         <v>0.1</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3316,7 +3307,7 @@
         <v>25.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
@@ -3324,8 +3315,8 @@
       <c r="Q34" s="3" t="n">
         <v>30.5</v>
       </c>
-      <c r="R34" s="8" t="n">
-        <v>35.8</v>
+      <c r="R34" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>30.2</v>
@@ -3349,7 +3340,7 @@
         <v>82</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3365,9 +3356,9 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>353.1</v>
-      </c>
-      <c r="D35" s="8" t="n">
+        <v>353.4</v>
+      </c>
+      <c r="D35" s="3" t="n">
         <v>31.1</v>
       </c>
       <c r="E35" s="3" t="n">
@@ -3401,7 +3392,7 @@
         <v>25.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>297.2</v>
+        <v>97.2</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0.7</v>
@@ -3409,11 +3400,11 @@
       <c r="Q35" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="R35" s="8" t="n">
-        <v>46.9</v>
+      <c r="R35" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>27.8</v>
+        <v>27.5</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>61.3</v>
@@ -3424,14 +3415,14 @@
       <c r="V35" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="W35" s="8" t="n">
-        <v>16.6</v>
+      <c r="W35" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>77.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8.4</v>
@@ -3450,7 +3441,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>430.7</v>
+        <v>30.7</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>32.1</v>
@@ -3516,10 +3507,10 @@
         <v>28.3</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>172</v>
+        <v>72</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3538,10 +3529,10 @@
         <v>1693.7</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>14155.4</v>
+        <v>155.4</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>102</v>
+        <v>102.2</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>128.7</v>
@@ -3562,7 +3553,7 @@
         <v>35.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>1106</v>
+        <v>106</v>
       </c>
       <c r="M37" s="3" t="n">
         <v>105.2</v>
@@ -3583,13 +3574,13 @@
         <v>126.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>1143.1</v>
+        <v>143.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>2324.8</v>
+        <v>324.8</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>79.7</v>
+        <v>77.7</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>136.8</v>
@@ -3601,10 +3592,10 @@
         <v>122.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>392.2</v>
+        <v>398.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>139.7</v>
+        <v>39.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3623,7 +3614,7 @@
         <v>338.7</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>31.9</v>
+        <v>31</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>20.4</v>
@@ -3654,7 +3645,7 @@
         <v>24.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>0.3</v>
@@ -3675,7 +3666,7 @@
         <v>15.5</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>27.4</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>24.3</v>
@@ -3684,7 +3675,7 @@
         <v>28.5</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>29.1</v>
+        <v>78</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>7.9</v>
@@ -3727,7 +3718,7 @@
         <v>3</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>21</v>
@@ -3754,10 +3745,10 @@
         <v>29.8</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>163.2</v>
+        <v>63.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>18.3</v>
+        <v>17.3</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>24.7</v>
@@ -3772,7 +3763,7 @@
         <v>88.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>23.6</v>
+        <v>3.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3788,7 +3779,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1453.7</v>
+        <v>453.7</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>32.9</v>
@@ -3806,7 +3797,7 @@
         <v>18.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.7</v>
+        <v>22.7</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>5</v>
@@ -3875,7 +3866,7 @@
       <c r="C41" s="3" t="n">
         <v>265.6</v>
       </c>
-      <c r="D41" s="8" t="n">
+      <c r="D41" s="3" t="n">
         <v>31.6</v>
       </c>
       <c r="E41" s="3" t="n">
@@ -3929,8 +3920,8 @@
       <c r="U41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="V41" s="8" t="n">
-        <v>11.6</v>
+      <c r="V41" s="3" t="n">
+        <v>24.6</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>23.4</v>
@@ -3939,7 +3930,7 @@
         <v>28</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>190.5</v>
+        <v>90.5</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>2.9</v>
@@ -3994,7 +3985,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.2</v>
@@ -4009,13 +4000,13 @@
         <v>29.3</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>97.2</v>
+        <v>97.7</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>24.7</v>
+        <v>22.7</v>
       </c>
       <c r="W42" s="3" t="n">
         <v>23.5</v>
@@ -4089,7 +4080,7 @@
         <v>25.5</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>30.4</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>75.59999999999999</v>
@@ -4129,7 +4120,7 @@
         <v>365.9</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>22.6</v>
+        <v>32.6</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>21.3</v>
@@ -4140,14 +4131,14 @@
       <c r="G44" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="H44" s="8" t="n">
-        <v>49.4</v>
+      <c r="H44" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>8.6</v>
+        <v>3.6</v>
       </c>
       <c r="K44" s="3" t="n">
         <v>0</v>
@@ -4183,19 +4174,19 @@
         <v>18.6</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>28.2</v>
+        <v>28.5</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>26.3</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>32.2</v>
+        <v>32.8</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>184.4</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4217,7 +4208,7 @@
         <v>190.6</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>1121.5</v>
+        <v>121.5</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>156.3</v>
@@ -4226,28 +4217,28 @@
         <v>69.09999999999999</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>1114.7</v>
+        <v>114.7</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>101.2</v>
+        <v>10.2</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>18.3</v>
+        <v>72.3</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>126.3</v>
+        <v>126.5</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>10122.9</v>
+        <v>125.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1148.7</v>
+        <v>148.7</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>293.8</v>
+        <v>593.8</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>1.3</v>
@@ -4262,7 +4253,7 @@
         <v>174.1</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>2430</v>
+        <v>250</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>68.59999999999999</v>
@@ -4274,10 +4265,10 @@
         <v>144.9</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>172.2</v>
+        <v>172.5</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>583.7</v>
+        <v>503.7</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>34</v>
@@ -4296,7 +4287,7 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>237.6</v>
+        <v>337.6</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>31.7</v>
@@ -4320,7 +4311,7 @@
         <v>3.1</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>21.1</v>
@@ -4337,11 +4328,11 @@
       <c r="P46" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q46" s="8" t="n">
+      <c r="Q46" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>21.8</v>
+        <v>24.8</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>29</v>
@@ -4362,7 +4353,7 @@
         <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>823.9</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>5.7</v>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_decimal_place_correction.xlsx
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>22.3</v>
+        <v>122.3</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>34.2</v>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>178.3</v>
+        <v>1783.5</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>164.8</v>
@@ -1185,7 +1185,7 @@
         <v>99.59999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>15.8</v>
+        <v>115.8</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>494.5</v>
@@ -1221,7 +1221,7 @@
         <v>388.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>41.6</v>
+        <v>22.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1260,7 +1260,9 @@
       <c r="J10" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>20</v>
       </c>
@@ -1408,7 +1410,7 @@
         <v>347.1</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>31.2</v>
+        <v>31.8</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>22.6</v>
@@ -2267,7 +2269,7 @@
         <v>27</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>11.8</v>
+        <v>118.2</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>19.8</v>
@@ -2282,7 +2284,7 @@
         <v>7.7</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>21.3</v>
+        <v>221.3</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>21</v>
@@ -2376,7 +2378,7 @@
         <v>126.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>489.4</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>2.2</v>
@@ -2644,7 +2646,7 @@
         <v>28</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>92</v>
+        <v>28.2</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>22.9</v>
@@ -2714,7 +2716,7 @@
         <v>24</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>98</v>
+        <v>198</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0.4</v>
@@ -2781,7 +2783,7 @@
         <v>18.9</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.8</v>
@@ -2802,7 +2804,7 @@
         <v>97.3</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>31.2</v>
@@ -2978,7 +2980,7 @@
         <v>135.8</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>120.7</v>
+        <v>1207.2</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>140.9</v>
@@ -2987,7 +2989,7 @@
         <v>396.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>126.1</v>
@@ -2999,7 +3001,7 @@
         <v>135.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>24.7</v>
+        <v>424.7</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>25.8</v>
@@ -3039,7 +3041,7 @@
         <v>1.4</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
@@ -3070,7 +3072,7 @@
         <v>79.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>25.2</v>
@@ -3222,7 +3224,7 @@
         <v>25.4</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>99.7</v>
+        <v>99</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>0.2</v>
@@ -3231,7 +3233,7 @@
         <v>28.9</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>22.6</v>
+        <v>24.6</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>28.2</v>
@@ -3416,13 +3418,13 @@
         <v>27.8</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>24.6</v>
+        <v>26.6</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>77.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8.4</v>
@@ -3441,7 +3443,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>30.7</v>
+        <v>430.7</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>32.1</v>
@@ -3532,7 +3534,7 @@
         <v>155.4</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>102.2</v>
+        <v>102</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>128.7</v>
@@ -3589,10 +3591,10 @@
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>122.4</v>
+        <v>142.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>398.2</v>
+        <v>392.2</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>39.7</v>
@@ -3675,7 +3677,7 @@
         <v>28.5</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>78</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>7.9</v>
@@ -3700,7 +3702,7 @@
         <v>31.9</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>20.2</v>
+        <v>220.2</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>26.1</v>
@@ -3718,7 +3720,7 @@
         <v>3</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>21</v>
@@ -3797,7 +3799,7 @@
         <v>18.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>22.7</v>
+        <v>2.7</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>5</v>
@@ -3970,7 +3972,7 @@
         <v>0.7</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>28.7</v>
@@ -4006,7 +4008,7 @@
         <v>0.7</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>22.7</v>
+        <v>24.7</v>
       </c>
       <c r="W42" s="3" t="n">
         <v>23.5</v>
@@ -4202,13 +4204,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>202.6</v>
+        <v>2026.2</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>190.6</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>121.5</v>
+        <v>1215.2</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>156.3</v>
@@ -4226,7 +4228,7 @@
         <v>18.4</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>72.3</v>
+        <v>78.3</v>
       </c>
       <c r="L45" s="3" t="n">
         <v>126.5</v>
@@ -4253,7 +4255,7 @@
         <v>174.1</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>68.59999999999999</v>
@@ -4329,7 +4331,7 @@
         <v>0.2</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>28.8</v>
+        <v>228.8</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>24.8</v>
@@ -4353,7 +4355,7 @@
         <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>5.7</v>

--- a/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/203/203_196905_SF.JPG_stage_decimal_place_correction.xlsx
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>122.3</v>
+        <v>422.3</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>34.2</v>
@@ -1136,7 +1136,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>20.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1783.5</v>
+        <v>178.3</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>164.8</v>
@@ -1221,7 +1221,7 @@
         <v>388.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>22.8</v>
+        <v>41.6</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1260,9 +1260,7 @@
       <c r="J10" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K10" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
         <v>20</v>
       </c>
@@ -1856,7 +1854,7 @@
         <v>3.9</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>22.1</v>
@@ -2269,7 +2267,7 @@
         <v>27</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>118.2</v>
+        <v>16.8</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>19.8</v>
@@ -2284,7 +2282,7 @@
         <v>7.7</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>221.3</v>
+        <v>21.3</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>21</v>
@@ -2646,10 +2644,10 @@
         <v>28</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>28.2</v>
+        <v>92</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>22.9</v>
+        <v>2</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>23.8</v>
@@ -2716,7 +2714,7 @@
         <v>24</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>0.4</v>
@@ -2783,7 +2781,7 @@
         <v>18.9</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.8</v>
@@ -2980,7 +2978,7 @@
         <v>135.8</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>1207.2</v>
+        <v>120.7</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>140.9</v>
@@ -2989,7 +2987,7 @@
         <v>396.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>26</v>
+        <v>10.5</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>126.1</v>
@@ -3020,7 +3018,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>211.2</v>
+        <v>21.1</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>29</v>
@@ -3041,7 +3039,7 @@
         <v>1.4</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
@@ -3072,7 +3070,7 @@
         <v>79.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>18.1</v>
+        <v>8.1</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>25.2</v>
@@ -3418,7 +3416,7 @@
         <v>27.8</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>26.6</v>
+        <v>24.6</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>28.9</v>
@@ -3546,7 +3544,7 @@
         <v>96.5</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>110.1</v>
+        <v>10.1</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>18.1</v>
@@ -3591,10 +3589,10 @@
         <v>121.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>142.4</v>
+        <v>182.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>392.2</v>
+        <v>398.2</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>39.7</v>
@@ -3702,7 +3700,7 @@
         <v>31.9</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>220.2</v>
+        <v>20.2</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>26.1</v>
@@ -3847,7 +3845,7 @@
         <v>26.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>10.4</v>
@@ -4204,13 +4202,13 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2026.2</v>
+        <v>202.6</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>190.6</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>1215.2</v>
+        <v>121.5</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>156.3</v>
@@ -4313,7 +4311,7 @@
         <v>3.1</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>21.1</v>
@@ -4331,7 +4329,7 @@
         <v>0.2</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>228.8</v>
+        <v>28.8</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>24.8</v>
@@ -4355,7 +4353,7 @@
         <v>28.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>83.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>5.7</v>
